--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86694A0F-CEF2-424D-B1D8-CF76E8E7DAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93735117-5662-4D5E-B51E-847CDB303717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="562">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1636,6 +1636,156 @@
   </si>
   <si>
     <t>documents\meeting minutes\OAC\Meeting_Minutes_OAC-001_2026-10-01_Rev1.pdf</t>
+  </si>
+  <si>
+    <t>SUB-001</t>
+  </si>
+  <si>
+    <t>23 0503</t>
+  </si>
+  <si>
+    <t>HVAC Package Rev 0 (Procore 230503-1.0 / Fieldwire PSI-0004) - Lennox RTUs &amp; mini-split, CaptiveAire, ductwork, Greenheck/Titus &amp; Fantech/Airius air distribution, prelim TAB. Reviewer: Make Corrections Noted 9/14 - provide missing EF-1 &amp; air terminal info (addressed in Rev 1). Req'd return = 14-day default; Procore had no due date.</t>
+  </si>
+  <si>
+    <t>Product Data</t>
+  </si>
+  <si>
+    <t>Platinum Air Systems</t>
+  </si>
+  <si>
+    <t>Approved as Noted</t>
+  </si>
+  <si>
+    <t>SUB-001_R1_Original_Procore_Export_2026-10-01.pdf; Submittal-001_Transmittal_Packaged.pdf (package INCLUDED, 659 pp); SUB-001_R0_Reviewed_MakeCorrectionsNoted_2026-09-14.pdf; SUB-001_R1_Reviewed_MakeCorrectionsNoted_2026-09-28.pdf; SUB-001_R1_As-Submitted_PSI-0004_2026-09-22.pdf - folder: documents\submittals\SUB-001 - 230503 HVAC</t>
+  </si>
+  <si>
+    <t>SUB-001-R1</t>
+  </si>
+  <si>
+    <t>HVAC Package Rev 1 (Procore 230503-1.1) - corrections made; EF-1 (SE1-10-440-VG) &amp; Titus air terminals added. Reviewer: Make Corrections Noted 9/28 - OPEN: provide TG-1 per plans and diffuser/register/grille schedule. Procore still Open, ball in court Amy Schoch (Progressive).</t>
+  </si>
+  <si>
+    <t>SUB-002</t>
+  </si>
+  <si>
+    <t>33 4100</t>
+  </si>
+  <si>
+    <t>Stormwater Package Rev 0 (Procore 33 4100-2.0 / Fieldwire PSI-0002) - Hydro International First Defense hydrodynamic separator (ST8), Up-Flo water quality filter (ST5), Southeast Culvert 84in CMP underground detention. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/9; Procore has no due date.</t>
+  </si>
+  <si>
+    <t>Coles Construction</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>SUB-002_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-002_Transmittal_Packaged.pdf (package INCLUDED, 62 pp) - folder: documents\submittals\SUB-002 - 334100 Storm Drainage</t>
+  </si>
+  <si>
+    <t>SUB-003</t>
+  </si>
+  <si>
+    <t>Coles Construction (supplier Core &amp; Main)</t>
+  </si>
+  <si>
+    <t>SUB-003_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-003_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-003 - 334100 Site Utilities</t>
+  </si>
+  <si>
+    <t>HDPE Pipe Rev 0 (Procore 33 4100-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - ADS N-12 ST IB storm pipe (pkg Section 1). Attachment is the full Core &amp; Main site utility package; Procore splits Package #1 into one item per spec section (sanitary = SUB-004). Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
+  </si>
+  <si>
+    <t>SUB-004</t>
+  </si>
+  <si>
+    <t>33 3000</t>
+  </si>
+  <si>
+    <t>Sanitary Sewer Rev 0 (Procore 33 3000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - Diamond Sani-21 PVC sewer pipe &amp; fittings, cleanouts, Star Pipe heavy-duty covers, marking tape (pkg Section 2, export pp. 8-19). Same PSI-0001 attachment as SUB-003. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
+  </si>
+  <si>
+    <t>SUB-004_R0_Original_Procore_Export_2026-10-01.pdf; SUB-004_R0_Sanitary_Section_Only.pdf; Submittal-004_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-004 - 333000 Sanitary Sewer</t>
+  </si>
+  <si>
+    <t>SUB-005</t>
+  </si>
+  <si>
+    <t>33 1000</t>
+  </si>
+  <si>
+    <t>Domestic Water &amp; Irrigation Rev 0 (Procore 33 1000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - PVC pressure pipe &amp; DI fittings, 2in tap assemblies (Smith-Blair 313, Ford Meter Box), 2in DCV (Wilkins 950XLT), irrigation, 2in RPZ (Wilkins 975XL2) (pkg Section 3, export pp. 20-53). Same PSI-0001 attachment as SUB-003/004. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
+  </si>
+  <si>
+    <t>SUB-005_R0_Original_Procore_Export_2026-10-01.pdf; SUB-005_R0_Domestic_Water_Section_Only.pdf; Submittal-005_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-005 - 331000 Domestic Water</t>
+  </si>
+  <si>
+    <t>SUB-006</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Fire Main Rev 0 (Procore 33-1.0, Package #1 Site Utilities) - U.S. Pipe Tyton DI pipe &amp; fittings, tapping sleeve, M&amp;H 129 hydrant, 8in DCDA BFP vault (Wilkins 350ASTDA), 8in PIV, 8in gate valve (PSI-0001 pkg Section 4, export pp. 54-91). FLAG: Procore item has NO ATTACHMENT (cover only) and spec is division-level '33 - Utilities' - confirm CHA has the fire main cut sheets. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11.</t>
+  </si>
+  <si>
+    <t>SUB-006_R0_Procore_Cover_Only_2026-10-01.pdf (Procore item has NO attachment); SUB-006_R0_Fire_Main_Section_REFERENCE_from_PSI-0001.pdf (from SUB-003 copy); Submittal-006_Transmittal_Packaged.pdf (42 pp) - folder: documents\submittals\SUB-006 - 33 Fire Main</t>
+  </si>
+  <si>
+    <t>SUB-007</t>
+  </si>
+  <si>
+    <t>22 (22 1119)</t>
+  </si>
+  <si>
+    <t>Plumbing Package Rev 0 (Procore 22-1.0, Package #2 Plumbing / Fieldwire PSI-0003) - fixtures (DF, L, WC, SK-1/2/3), hydrants, floor drains/sinks, PRV, EWH-1, gas meter. Procore CLOSED. Reviewer (Progressive, bizons 9/25): Make Corrections Noted - OPEN: SK-3 replace Elkay SS8354LR4 with Elkay 14-3C16X20-L-18X per CCD 01 (05/28/2026). Returned 14 days after 9/11 due date.</t>
+  </si>
+  <si>
+    <t>Golden Hands Plumbing (supplier Cowan Supply)</t>
+  </si>
+  <si>
+    <t>SUB-007_R0_Original_Procore_Export_2026-10-01.pdf; SUB-007_R0_Reviewed_MakeCorrectionsNoted_2026-09-25.pdf; SUB-007_R0_As-Submitted_PSI-0003_2026-09-03.pdf; Submittal-007_Transmittal_Packaged.pdf (package INCLUDED, 217 pp) - folder: documents\submittals\SUB-007 - 22 Plumbing</t>
+  </si>
+  <si>
+    <t>SUB-008</t>
+  </si>
+  <si>
+    <t>None (Procore '1 - Default')</t>
+  </si>
+  <si>
+    <t>CCTV Submittal Rev 0 (Procore 1-3.0 / Fieldwire PSI-0007) - off-site traffic signal Gwinnett Co. TS-082, Jimmy Carter Blvd @ Shelby Dr: AXIS Q6086-E PTZ camera, Major Custom Cable CAT6 100ft, DITEK DTK-MRJPOES surge protector, AXIS TQ5001-E mount (Utilicom quote 62085). No spec section assigned. Reviewer: CHA Consulting (Christopher Manes) - no response; confirm whether Gwinnett DOT review also required. Req'd return per Fieldwire response due 9/25.</t>
+  </si>
+  <si>
+    <t>R.J. Haynie &amp; Associates (supplier Utilicom Supply Associates)</t>
+  </si>
+  <si>
+    <t>SUB-008_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-008_Transmittal_Packaged.pdf (package INCLUDED, 18 pp) - folder: documents\submittals\SUB-008 - CCTV Traffic Signal</t>
+  </si>
+  <si>
+    <t>SUB-009</t>
+  </si>
+  <si>
+    <t>Mast Arm Pole Shop Drawings #1-#3 Rev 0 (Procore 1-2.0 / Fieldwire PSI-0006) - off-site traffic signal Gwinnett Co. TS-082, Jimmy Carter Blvd @ Shelby Dr: Valmont GA672263P1 (2 sheets, GA PE sealed 8/31) Poles B (22ft, 65+55ft arms) &amp; C (30ft, 55+55ft arms) + orientation sketch. FLAG: foundation callout (3ft dia x 14.5ft, (8) #10) is an unsigned annotation, not on sealed dwg - verify. Reviewer: CHA Consulting (Christopher Manes) - no response; confirm Gwinnett DOT review. Req'd return per Fieldwire due 9/25.</t>
+  </si>
+  <si>
+    <t>Shop Drawing</t>
+  </si>
+  <si>
+    <t>R.J. Haynie &amp; Associates (Valmont via DOT Lighting / Traffic &amp; Lighting Corp)</t>
+  </si>
+  <si>
+    <t>SUB-009_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-009_Transmittal_Packaged.pdf (package INCLUDED, 6 pp) - folder: documents\submittals\SUB-009 - Mast Arm Poles</t>
+  </si>
+  <si>
+    <t>SUB-010</t>
+  </si>
+  <si>
+    <t>Mast Arm Pole Submittals Rev 0 (Procore 1-1.0 / Fieldwire PSI-0005) - Valmont structural calcs, Order 672263-P1 (94 pp), Poles B (P22 M65/M55) &amp; C (P30 M55/M55), AASHTO 2015, 115 mph - off-site signal Gwinnett Co. TS-082. Related to SUB-009 shop dwgs. FLAG: calcs give foundation reactions only, no foundation design; PE seal is image stamp, not digitally signed. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire due 9/25.</t>
+  </si>
+  <si>
+    <t>R.J. Haynie &amp; Associates (Valmont Industries)</t>
+  </si>
+  <si>
+    <t>SUB-010_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-010_Transmittal_Packaged.pdf (package INCLUDED, 99 pp) - folder: documents\submittals\SUB-010 - Mast Arm Pole Calcs</t>
   </si>
 </sst>
 </file>
@@ -1782,7 +1932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1816,6 +1966,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18161,7 +18312,7 @@
       </c>
       <c r="C15" s="4">
         <f>COUNTIFS('Submittal Log'!G2:G299,"&lt;&gt;",'Submittal Log'!I2:I299,"")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
@@ -18461,7 +18612,7 @@
       </c>
       <c r="C52" s="4">
         <f ca="1">COUNTIF('Submittal Log'!P2:P299,"&gt;=14")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -24423,13 +24574,49 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K2" t="str">
+      <c r="A2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F2" s="25">
+        <v>46268</v>
+      </c>
+      <c r="G2" s="25">
+        <v>46274</v>
+      </c>
+      <c r="H2" s="25">
+        <v>46288</v>
+      </c>
+      <c r="I2" s="25">
+        <v>46289</v>
+      </c>
+      <c r="J2" t="s">
+        <v>517</v>
+      </c>
+      <c r="K2">
         <f t="shared" ref="K2:K65" ca="1" si="0">IF(A2="","",IF(I2&lt;&gt;"",I2-G2,IF(G2&lt;&gt;"",TODAY()-G2,"")))</f>
-        <v/>
-      </c>
-      <c r="O2" s="13" t="str">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O2" s="13">
         <f t="shared" ref="O2:O65" si="1">IF(A2="","",MAX(F2+0,G2+0,H2+0,I2+0))</f>
-        <v/>
+        <v>46289</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P65" ca="1" si="2">IF(A2="","",IF(OR(J2="Approved",J2="Approved as Noted"),"",TODAY()-O2))</f>
@@ -24437,13 +24624,49 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K3" t="str">
+      <c r="A3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F3" s="25">
+        <v>46287</v>
+      </c>
+      <c r="G3" s="25">
+        <v>46287</v>
+      </c>
+      <c r="H3" s="25">
+        <v>46309</v>
+      </c>
+      <c r="I3" s="25">
+        <v>46293</v>
+      </c>
+      <c r="J3" t="s">
+        <v>517</v>
+      </c>
+      <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O3" s="13" t="str">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>518</v>
+      </c>
+      <c r="N3" t="s">
+        <v>274</v>
+      </c>
+      <c r="O3" s="13">
         <f t="shared" si="1"/>
-        <v/>
+        <v>46309</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24451,83 +24674,284 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K4" t="str">
+      <c r="A4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F4" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G4" s="25">
+        <v>46260</v>
+      </c>
+      <c r="H4" s="25">
+        <v>46274</v>
+      </c>
+      <c r="J4" t="s">
+        <v>525</v>
+      </c>
+      <c r="K4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O4" s="13" t="str">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>526</v>
+      </c>
+      <c r="N4" t="s">
+        <v>274</v>
+      </c>
+      <c r="O4" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P4" t="str">
+        <v>46274</v>
+      </c>
+      <c r="P4">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K5" t="str">
+      <c r="A5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="C5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D5" t="s">
+        <v>515</v>
+      </c>
+      <c r="E5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F5" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G5" s="25">
+        <v>46260</v>
+      </c>
+      <c r="H5" s="25">
+        <v>46276</v>
+      </c>
+      <c r="J5" t="s">
+        <v>525</v>
+      </c>
+      <c r="K5">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O5" s="13" t="str">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>529</v>
+      </c>
+      <c r="N5" t="s">
+        <v>274</v>
+      </c>
+      <c r="O5" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P5" t="str">
+        <v>46276</v>
+      </c>
+      <c r="P5">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K6" t="str">
+      <c r="A6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C6" t="s">
+        <v>533</v>
+      </c>
+      <c r="D6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F6" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G6" s="25">
+        <v>46260</v>
+      </c>
+      <c r="H6" s="25">
+        <v>46276</v>
+      </c>
+      <c r="J6" t="s">
+        <v>525</v>
+      </c>
+      <c r="K6">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O6" s="13" t="str">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>534</v>
+      </c>
+      <c r="N6" t="s">
+        <v>274</v>
+      </c>
+      <c r="O6" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P6" t="str">
+        <v>46276</v>
+      </c>
+      <c r="P6">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K7" t="str">
+      <c r="A7" t="s">
+        <v>535</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E7" t="s">
+        <v>528</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G7" s="25">
+        <v>46260</v>
+      </c>
+      <c r="H7" s="25">
+        <v>46276</v>
+      </c>
+      <c r="J7" t="s">
+        <v>525</v>
+      </c>
+      <c r="K7">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O7" s="13" t="str">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>538</v>
+      </c>
+      <c r="N7" t="s">
+        <v>274</v>
+      </c>
+      <c r="O7" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P7" t="str">
+        <v>46276</v>
+      </c>
+      <c r="P7">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K8" t="str">
+      <c r="A8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="C8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E8" t="s">
+        <v>528</v>
+      </c>
+      <c r="F8" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G8" s="25">
+        <v>46260</v>
+      </c>
+      <c r="H8" s="25">
+        <v>46276</v>
+      </c>
+      <c r="J8" t="s">
+        <v>525</v>
+      </c>
+      <c r="K8">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O8" s="13" t="str">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>542</v>
+      </c>
+      <c r="N8" t="s">
+        <v>274</v>
+      </c>
+      <c r="O8" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P8" t="str">
+        <v>46276</v>
+      </c>
+      <c r="P8">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K9" t="str">
+      <c r="A9" t="s">
+        <v>543</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="C9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D9" t="s">
+        <v>515</v>
+      </c>
+      <c r="E9" t="s">
+        <v>546</v>
+      </c>
+      <c r="F9" s="25">
+        <v>46260</v>
+      </c>
+      <c r="G9" s="25">
+        <v>46268</v>
+      </c>
+      <c r="H9" s="25">
+        <v>46276</v>
+      </c>
+      <c r="I9" s="25">
+        <v>46290</v>
+      </c>
+      <c r="J9" t="s">
+        <v>517</v>
+      </c>
+      <c r="K9">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O9" s="13" t="str">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>547</v>
+      </c>
+      <c r="N9" t="s">
+        <v>274</v>
+      </c>
+      <c r="O9" s="13">
         <f t="shared" si="1"/>
-        <v/>
+        <v>46290</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24535,45 +24959,144 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K10" t="str">
+      <c r="A10" t="s">
+        <v>548</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="C10" t="s">
+        <v>550</v>
+      </c>
+      <c r="D10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" t="s">
+        <v>551</v>
+      </c>
+      <c r="F10" s="25">
+        <v>46265</v>
+      </c>
+      <c r="G10" s="25">
+        <v>46283</v>
+      </c>
+      <c r="H10" s="25">
+        <v>46290</v>
+      </c>
+      <c r="J10" t="s">
+        <v>525</v>
+      </c>
+      <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O10" s="13" t="str">
+        <v>13</v>
+      </c>
+      <c r="M10" t="s">
+        <v>552</v>
+      </c>
+      <c r="N10" t="s">
+        <v>274</v>
+      </c>
+      <c r="O10" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P10" t="str">
+        <v>46290</v>
+      </c>
+      <c r="P10">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K11" t="str">
+      <c r="A11" t="s">
+        <v>553</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="C11" t="s">
+        <v>554</v>
+      </c>
+      <c r="D11" t="s">
+        <v>555</v>
+      </c>
+      <c r="E11" t="s">
+        <v>556</v>
+      </c>
+      <c r="F11" s="25">
+        <v>46265</v>
+      </c>
+      <c r="G11" s="25">
+        <v>46283</v>
+      </c>
+      <c r="H11" s="25">
+        <v>46290</v>
+      </c>
+      <c r="J11" t="s">
+        <v>525</v>
+      </c>
+      <c r="K11">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O11" s="13" t="str">
+        <v>13</v>
+      </c>
+      <c r="M11" t="s">
+        <v>557</v>
+      </c>
+      <c r="N11" t="s">
+        <v>274</v>
+      </c>
+      <c r="O11" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P11" t="str">
+        <v>46290</v>
+      </c>
+      <c r="P11">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K12" t="str">
+      <c r="A12" t="s">
+        <v>558</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="C12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D12" t="s">
+        <v>515</v>
+      </c>
+      <c r="E12" t="s">
+        <v>560</v>
+      </c>
+      <c r="F12" s="25">
+        <v>46265</v>
+      </c>
+      <c r="G12" s="25">
+        <v>46283</v>
+      </c>
+      <c r="H12" s="25">
+        <v>46290</v>
+      </c>
+      <c r="J12" t="s">
+        <v>525</v>
+      </c>
+      <c r="K12">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="O12" s="13" t="str">
+        <v>13</v>
+      </c>
+      <c r="M12" t="s">
+        <v>561</v>
+      </c>
+      <c r="N12" t="s">
+        <v>274</v>
+      </c>
+      <c r="O12" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P12" t="str">
+        <v>46290</v>
+      </c>
+      <c r="P12">
         <f t="shared" ca="1" si="2"/>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">

--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93735117-5662-4D5E-B51E-847CDB303717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95BC9F3-88BD-4A5A-9911-60C6C5875E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1215" yWindow="4035" windowWidth="28800" windowHeight="17145" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="580">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1786,6 +1786,60 @@
   </si>
   <si>
     <t>SUB-010_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-010_Transmittal_Packaged.pdf (package INCLUDED, 99 pp) - folder: documents\submittals\SUB-010 - Mast Arm Pole Calcs</t>
+  </si>
+  <si>
+    <t>PCO-001</t>
+  </si>
+  <si>
+    <t>Owner Request</t>
+  </si>
+  <si>
+    <t>Earthwork/Site Utilities, Roofing, Low Voltage, Metal Panels, Plumbing, Rooftop Screens, Doors/Frames/Hardware</t>
+  </si>
+  <si>
+    <t>OCO-01</t>
+  </si>
+  <si>
+    <t>Base bid material/fuel price escalation true-up (Q1 2026 bid to July 2026 award); 5% OH&amp;P</t>
+  </si>
+  <si>
+    <t>CO #01 - OCO Package - Pricing Escalation Rebalance.pdf (incl. PSI PCO-001 cost breakdown); 22_GC_CO_Template - CO01 rev1.xlsx; OCO #01 - Email Backup (7/29-8/3/2026)</t>
+  </si>
+  <si>
+    <t>SCO-LOG-001</t>
+  </si>
+  <si>
+    <t>CO-02 Asbestos abatement (Georgia Environmental): Main Event Hall ACM floor mastic/carpet glue/carpet + ACM roofing mastic at 8 roof vents</t>
+  </si>
+  <si>
+    <t>PCO-002 / OCO-02</t>
+  </si>
+  <si>
+    <t>PCO-002</t>
+  </si>
+  <si>
+    <t>Allowance #01 - building demolition + ACM abatement; $224,903.34 drawn from $225,000 Demolition Allowance ($96.66 remaining); net $0 to Contract Sum; 9.8% GC OH&amp;P</t>
+  </si>
+  <si>
+    <t>OCO-02</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Luis Marcelino, General Manager</t>
+  </si>
+  <si>
+    <t>Lidl #1517 - Change Order #2 - Asbestos Abatement.pdf; SCO - Coles Construction CO-02.xlsx</t>
+  </si>
+  <si>
+    <t>Valid change: Subcontract No. 7 (8/4/2026) Exhibit A covers selective/building demolition but no asbestos/ACM abatement, and PSI's bid (exclusion h) excludes asbestos abatement. ACM black floor mastic and roof penetration cement are confirmed in Owner's NOVA pre-demolition ACM survey (3/18/2021). Sub O&amp;P 10% = prime contract 4.2 sub cap. Optional $5,500 debris line excluded (debris to be cleared before mobilization). Additional unsampled roof/mirror glue ACM to come as a separate SCO. Approved contingent on Lidl executing CO #02.</t>
+  </si>
+  <si>
+    <t>CO #02 - OCO Package - Building Demolition &amp; Abatement.pdf; Lidl 1517 Demolition Scope.pdf (Cole's demo proposal $148,400); SCO - Coles Construction CO-02.xlsx; Lidl #1517 - Change Order #2 - Asbestos Abatement.pdf (Cole's CO-02 / SCO-LOG-001); 22_GC_CO_Template - CO02.xlsx</t>
+  </si>
+  <si>
+    <t>Demolition (Building &amp; Site), Asbestos Abatement</t>
   </si>
 </sst>
 </file>
@@ -18336,7 +18390,7 @@
       </c>
       <c r="C18" s="4">
         <f>COUNTIF('Change Order Log'!J2:J299,"Pending")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -18378,7 +18432,7 @@
       </c>
       <c r="C23" s="17">
         <f>SUMIFS('Subcontractor CO Log'!N2:N299,'Subcontractor CO Log'!K2:K299,"Approved")</f>
-        <v>0</v>
+        <v>56430</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -18621,7 +18675,7 @@
       </c>
       <c r="C53" s="4">
         <f ca="1">COUNTIF('Change Order Log'!Q2:Q299,"&gt;=14")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
@@ -29213,31 +29267,97 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M2" t="str">
+      <c r="A2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B2" s="25">
+        <v>46254</v>
+      </c>
+      <c r="C2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E2" t="s">
+        <v>564</v>
+      </c>
+      <c r="H2">
+        <v>99986.52</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>525</v>
+      </c>
+      <c r="M2">
         <f>IF(A2="","",SUMIFS(H$2:H2,J$2:J2,"Approved"))</f>
-        <v/>
-      </c>
-      <c r="P2" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>567</v>
+      </c>
+      <c r="O2" t="s">
+        <v>274</v>
+      </c>
+      <c r="P2" s="13">
         <f t="shared" ref="P2:P65" si="0">IF(A2="","",MAX(B2+0,K2+0,L2+0))</f>
-        <v/>
-      </c>
-      <c r="Q2" t="str">
+        <v>46254</v>
+      </c>
+      <c r="Q2">
         <f t="shared" ref="Q2:Q65" ca="1" si="1">IF(A2="","",IF(OR(J2="Approved",J2="Rejected",J2="Void"),"",TODAY()-P2))</f>
-        <v/>
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M3" t="str">
+      <c r="A3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B3" s="25">
+        <v>46259</v>
+      </c>
+      <c r="C3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E3" t="s">
+        <v>579</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>525</v>
+      </c>
+      <c r="M3">
         <f>IF(A3="","",SUMIFS(H$2:H3,J$2:J3,"Approved"))</f>
-        <v/>
-      </c>
-      <c r="P3" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>578</v>
+      </c>
+      <c r="O3" t="s">
+        <v>274</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Q3" t="str">
+        <v>46259</v>
+      </c>
+      <c r="Q3">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>37</v>
+      </c>
+      <c r="R3" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -33490,13 +33610,58 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="O2" t="str">
+      <c r="A2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B2" s="25">
+        <v>46257</v>
+      </c>
+      <c r="C2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F2">
+        <v>56430</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J2" t="s">
+        <v>577</v>
+      </c>
+      <c r="K2" t="s">
+        <v>574</v>
+      </c>
+      <c r="L2" s="25">
+        <v>46296</v>
+      </c>
+      <c r="M2" t="s">
+        <v>575</v>
+      </c>
+      <c r="N2">
+        <v>56430</v>
+      </c>
+      <c r="O2">
         <f>IF(C2="","",SUMIFS($N$2:N2,$C$2:C2,C2,$K$2:K2,"Approved"))</f>
-        <v/>
-      </c>
-      <c r="R2" s="13" t="str">
+        <v>56430</v>
+      </c>
+      <c r="P2" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>274</v>
+      </c>
+      <c r="R2" s="13">
         <f t="shared" ref="R2:R65" si="0">IF(C2="","",MAX(B2+0,L2+0))</f>
-        <v/>
+        <v>46296</v>
       </c>
       <c r="S2" t="str">
         <f t="shared" ref="S2:S65" ca="1" si="1">IF(C2="","",IF(OR(K2="Approved",K2="Rejected",K2="Void"),"",TODAY()-R2))</f>

--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95BC9F3-88BD-4A5A-9911-60C6C5875E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B48CE0-B4D4-44E3-BC8F-685381009B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="4035" windowWidth="28800" windowHeight="17145" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3210" windowWidth="28800" windowHeight="17145" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="610">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1840,6 +1840,96 @@
   </si>
   <si>
     <t>Demolition (Building &amp; Site), Asbestos Abatement</t>
+  </si>
+  <si>
+    <t>E101</t>
+  </si>
+  <si>
+    <t>Ground Floor - Electrical Power Plan</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Issued for Bid (Bid Set, Permit Cycle 2)</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative)</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: undershelf lighting power, refrig/freezer layout, produce power poles, ADA scooter power relocated</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: digital sign power, 2 receptacles on LC1-38 (Vestibule), keynote 22</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD1.pdf; E-DWGs_CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>E300</t>
+  </si>
+  <si>
+    <t>Enlarged Electrical Drawings (Bakery / Technical)</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: oven keynote revised to 2x NEMA 15-60R (lower) + 2x 15-50R (upper)</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>E301</t>
+  </si>
+  <si>
+    <t>Enlarged Electrical Drawings (Checkout / Cooler-Freezer)</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: freezer layout &amp; connections, cooler layout added, checkout power updated</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: digital sign power, 2 receptacles on LC1-40 (checkout storefront), keynote 19</t>
+  </si>
+  <si>
+    <t>E501</t>
+  </si>
+  <si>
+    <t>Electrical Panel Schedules</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: step-down transformer breakers; bakery oven breakers 20A to 60A/3P</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: upper ovens 50A/3P (BK1-13, 25), lower 60A/3P (BK1-19, 31); BK1 57.8 kVA</t>
+  </si>
+  <si>
+    <t>E502</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: LA2 panel schedule updated</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: LC1-38 / LC1-40 spares become Digital Signage, 720 VA each</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
+    <t>Ground Floor - Technology Plan</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: checkout data locations updated; hand hole shifted</t>
+  </si>
+  <si>
+    <t>2026-07-30 — CCD 02: 3 data outlets for digital signs, keynote 30 (vestibule outlet not clouded)</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - T-DWGs_Bid Set.pdf; T-DWGs_CCD1.pdf; T101-CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
   </si>
 </sst>
 </file>
@@ -17336,6 +17426,207 @@
         <v>226</v>
       </c>
     </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C5" t="s">
+        <v>582</v>
+      </c>
+      <c r="D5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" t="s">
+        <v>584</v>
+      </c>
+      <c r="F5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G5" t="s">
+        <v>586</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L5" t="s">
+        <v>587</v>
+      </c>
+      <c r="M5" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C6" t="s">
+        <v>582</v>
+      </c>
+      <c r="D6" t="s">
+        <v>583</v>
+      </c>
+      <c r="E6" t="s">
+        <v>591</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L6" t="s">
+        <v>587</v>
+      </c>
+      <c r="M6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D7" t="s">
+        <v>583</v>
+      </c>
+      <c r="E7" t="s">
+        <v>584</v>
+      </c>
+      <c r="F7" t="s">
+        <v>595</v>
+      </c>
+      <c r="G7" t="s">
+        <v>596</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L7" t="s">
+        <v>587</v>
+      </c>
+      <c r="M7" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>597</v>
+      </c>
+      <c r="B8" t="s">
+        <v>598</v>
+      </c>
+      <c r="C8" t="s">
+        <v>582</v>
+      </c>
+      <c r="D8" t="s">
+        <v>583</v>
+      </c>
+      <c r="E8" t="s">
+        <v>599</v>
+      </c>
+      <c r="F8" t="s">
+        <v>600</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L8" t="s">
+        <v>587</v>
+      </c>
+      <c r="M8" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B9" t="s">
+        <v>598</v>
+      </c>
+      <c r="C9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D9" t="s">
+        <v>583</v>
+      </c>
+      <c r="E9" t="s">
+        <v>584</v>
+      </c>
+      <c r="F9" t="s">
+        <v>602</v>
+      </c>
+      <c r="G9" t="s">
+        <v>603</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L9" t="s">
+        <v>587</v>
+      </c>
+      <c r="M9" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>604</v>
+      </c>
+      <c r="B10" t="s">
+        <v>605</v>
+      </c>
+      <c r="C10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D10" t="s">
+        <v>583</v>
+      </c>
+      <c r="E10" t="s">
+        <v>584</v>
+      </c>
+      <c r="F10" t="s">
+        <v>607</v>
+      </c>
+      <c r="G10" t="s">
+        <v>608</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L10" t="s">
+        <v>587</v>
+      </c>
+      <c r="M10" t="s">
+        <v>609</v>
+      </c>
+    </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>435</v>

--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B48CE0-B4D4-44E3-BC8F-685381009B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439FE3C-2054-4CF5-9257-E0CFDD99812F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3210" windowWidth="28800" windowHeight="17145" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="907">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1866,9 +1866,6 @@
     <t>Current</t>
   </si>
   <si>
-    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD1.pdf; E-DWGs_CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
-  </si>
-  <si>
     <t>E300</t>
   </si>
   <si>
@@ -1878,9 +1875,6 @@
     <t>2026-07-30 — CCD 02: oven keynote revised to 2x NEMA 15-60R (lower) + 2x 15-50R (upper)</t>
   </si>
   <si>
-    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
-  </si>
-  <si>
     <t>E301</t>
   </si>
   <si>
@@ -1929,7 +1923,904 @@
     <t>2026-07-30 — CCD 02: 3 data outlets for digital signs, keynote 30 (vestibule outlet not clouded)</t>
   </si>
   <si>
-    <t>Lidl 1517 - T-DWGs_Bid Set.pdf; T-DWGs_CCD1.pdf; T101-CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
+    <t>G001</t>
+  </si>
+  <si>
+    <t>Cover Sheet</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>2025-12-17 — Issued for Bid (Bid Set, Permit Cycle 2)</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): special inspections note added; cover rendering shows straight vestibule storefront</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - G-DWGs_Bid Set.pdf; G-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>G101</t>
+  </si>
+  <si>
+    <t>General Notes</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): special inspections note added</t>
+  </si>
+  <si>
+    <t>G102</t>
+  </si>
+  <si>
+    <t>Architectural Site Plan</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - G-DWGs_Bid Set.pdf; G-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>G103</t>
+  </si>
+  <si>
+    <t>Architectural Site Details</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: vestibule storefront mullion moved (not clouded)</t>
+  </si>
+  <si>
+    <t>G104</t>
+  </si>
+  <si>
+    <t>Life Safety Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: egress paths redrawn for new fixture plan and bakery shift; vestibule 560 to 417 SF, Sales 14,961 to 15,095 SF</t>
+  </si>
+  <si>
+    <t>G105</t>
+  </si>
+  <si>
+    <t>Typical Accessibility Standards</t>
+  </si>
+  <si>
+    <t>2025-11-07 — Issued for Bid (Bid Set, Permit Cycle 1)</t>
+  </si>
+  <si>
+    <t>G106</t>
+  </si>
+  <si>
+    <t>Wall and Partition Types</t>
+  </si>
+  <si>
+    <t>G107</t>
+  </si>
+  <si>
+    <t>Rated Assemblies</t>
+  </si>
+  <si>
+    <t>G108</t>
+  </si>
+  <si>
+    <t>Comcheck</t>
+  </si>
+  <si>
+    <t>G109</t>
+  </si>
+  <si>
+    <t>National Account List and Responsibility Matrix</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>Floor Plan</t>
+  </si>
+  <si>
+    <t>Architectural</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: bakery west stub 2'-2 1/2" W, north wall +2.7 LF; vestibule storefront moved 7'-3" S to grid B (not clouded)</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - A-DWGs_Bid Set.pdf; A-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>Reflected Ceiling Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: bakery soffit moved 2'-2 3/8" W; sales/vestibule lighting re-laid; bakery return grilles 2 to 1</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>Roof Plan</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - A-DWGs_Bid Set.pdf; A-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>Building Outline Plan</t>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>Finish and RAM Protection Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: Sales/Vestibule paint P-1 to P-8 (P-8 undefined); vestibule storefront moved (not clouded)</t>
+  </si>
+  <si>
+    <t>A200</t>
+  </si>
+  <si>
+    <t>Exterior Elevations</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: FDC shown on elevation B2</t>
+  </si>
+  <si>
+    <t>A300</t>
+  </si>
+  <si>
+    <t>Building Sections</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: bakery case/soffit shift and dock guardrail shown in sections (not clouded)</t>
+  </si>
+  <si>
+    <t>A301</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: loading dock guardrail added in section B2 (not clouded)</t>
+  </si>
+  <si>
+    <t>A302</t>
+  </si>
+  <si>
+    <t>Wall Sections</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: vestibule relocation shown in section E5 (not clouded)</t>
+  </si>
+  <si>
+    <t>A303</t>
+  </si>
+  <si>
+    <t>A304</t>
+  </si>
+  <si>
+    <t>A305</t>
+  </si>
+  <si>
+    <t>A306</t>
+  </si>
+  <si>
+    <t>A400</t>
+  </si>
+  <si>
+    <t>Enlarged Plans &amp; Interior Elevations</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: bakery dims revised, SK-3 sink revised, FDC added on E7</t>
+  </si>
+  <si>
+    <t>A401</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): vestibule redesigned: straight storefront on grid B with 2 automatic sliders</t>
+  </si>
+  <si>
+    <t>A402</t>
+  </si>
+  <si>
+    <t>Interior Elevations</t>
+  </si>
+  <si>
+    <t>A403</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: paint P-1 to P-8 in B7, C7, E5, E4, E2; bakery sink and SS panel revised in A3</t>
+  </si>
+  <si>
+    <t>A404</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: paint P-1 to P-8 in B7, C7, D7, E7; D7 receptacles to surface raceway; E7 20'-0" to 27'-3"</t>
+  </si>
+  <si>
+    <t>A405</t>
+  </si>
+  <si>
+    <t>Interior Elevations (30% Owner Review)</t>
+  </si>
+  <si>
+    <t>2025-09-08 — Included in Bid Set (title block: 30% Owner Review)</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Not reissued in CCD 01 set; stray 30% Owner Review sheet, not for construction</t>
+  </si>
+  <si>
+    <t>Superseded</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - A-DWGs_Bid Set.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>A500</t>
+  </si>
+  <si>
+    <t>Interior Details</t>
+  </si>
+  <si>
+    <t>A501</t>
+  </si>
+  <si>
+    <t>A502</t>
+  </si>
+  <si>
+    <t>Casework Details</t>
+  </si>
+  <si>
+    <t>A600</t>
+  </si>
+  <si>
+    <t>Vertical Circulation</t>
+  </si>
+  <si>
+    <t>A601</t>
+  </si>
+  <si>
+    <t>Plan Details</t>
+  </si>
+  <si>
+    <t>A602</t>
+  </si>
+  <si>
+    <t>A603</t>
+  </si>
+  <si>
+    <t>A604</t>
+  </si>
+  <si>
+    <t>A605</t>
+  </si>
+  <si>
+    <t>Foundation Details</t>
+  </si>
+  <si>
+    <t>A606</t>
+  </si>
+  <si>
+    <t>Foundation and Sill Details</t>
+  </si>
+  <si>
+    <t>A607</t>
+  </si>
+  <si>
+    <t>Roof Section Details</t>
+  </si>
+  <si>
+    <t>A608</t>
+  </si>
+  <si>
+    <t>A609</t>
+  </si>
+  <si>
+    <t>Coping Details</t>
+  </si>
+  <si>
+    <t>A610</t>
+  </si>
+  <si>
+    <t>Roof Penetrations</t>
+  </si>
+  <si>
+    <t>A611</t>
+  </si>
+  <si>
+    <t>Exterior Details</t>
+  </si>
+  <si>
+    <t>A700</t>
+  </si>
+  <si>
+    <t>Window Elevations &amp; Details</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): Window 'C' deleted; Window 'A' bay C-B re-mullioned</t>
+  </si>
+  <si>
+    <t>A701</t>
+  </si>
+  <si>
+    <t>Storefront Details</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: vestibule storefront elevation updated (not clouded)</t>
+  </si>
+  <si>
+    <t>A702</t>
+  </si>
+  <si>
+    <t>Door Schedule and Elevations</t>
+  </si>
+  <si>
+    <t>A703</t>
+  </si>
+  <si>
+    <t>Door Details</t>
+  </si>
+  <si>
+    <t>A801</t>
+  </si>
+  <si>
+    <t>Fixture Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: supply-chain fixture plan replaced (4 checklanes, new cooler line, 10 RM meat case)</t>
+  </si>
+  <si>
+    <t>A802</t>
+  </si>
+  <si>
+    <t>Power Pole and Floor Drain Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: power poles 8 to 21 per new fixture plan</t>
+  </si>
+  <si>
+    <t>A803</t>
+  </si>
+  <si>
+    <t>Power Pole Details</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Structural</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - S-DWGs_Bid Set.pdf; S-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>Isometrics</t>
+  </si>
+  <si>
+    <t>S101</t>
+  </si>
+  <si>
+    <t>Ground Floor and Foundation Plan</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): vestibule HSS posts 4 to 2, 2 footings deleted, grid 2.3 deleted</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: building drain sleeve at dock wall</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - S-DWGs_Bid Set.pdf; S-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>S102</t>
+  </si>
+  <si>
+    <t>Roof Framing Plan</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): vestibule top beam relocated</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: bakery hanging CFMS wall relocated (39 to 34 LF), now off joist girder</t>
+  </si>
+  <si>
+    <t>S200</t>
+  </si>
+  <si>
+    <t>Structural Elevations</t>
+  </si>
+  <si>
+    <t>S300</t>
+  </si>
+  <si>
+    <t>Foundation and Concrete Details</t>
+  </si>
+  <si>
+    <t>S301</t>
+  </si>
+  <si>
+    <t>S400</t>
+  </si>
+  <si>
+    <t>Masonry Details</t>
+  </si>
+  <si>
+    <t>S500</t>
+  </si>
+  <si>
+    <t>Steel Details</t>
+  </si>
+  <si>
+    <t>S501</t>
+  </si>
+  <si>
+    <t>S502</t>
+  </si>
+  <si>
+    <t>S503</t>
+  </si>
+  <si>
+    <t>M000</t>
+  </si>
+  <si>
+    <t>Symbol List and General Notes - Mechanical</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - M-DWGs_Bid Set.pdf; M-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>M101</t>
+  </si>
+  <si>
+    <t>Mechanical Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: EF-1, TG-1 and thermostat added at Vestibule 100</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - M-DWGs_Bid Set.pdf; M-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>M102</t>
+  </si>
+  <si>
+    <t>Enlarged Mechanical Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: KEF-1 moved ~10" W; Bakery/Breakroom CRG-3 4 to 2</t>
+  </si>
+  <si>
+    <t>M103</t>
+  </si>
+  <si>
+    <t>Roof Mechanical Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: KEF-1 and roof curb moved ~10" W</t>
+  </si>
+  <si>
+    <t>M300</t>
+  </si>
+  <si>
+    <t>Mechanical Section Views</t>
+  </si>
+  <si>
+    <t>2025-11-07 — Included in Bid Set</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Not reissued in CCD 01 set; not on M000 sheet index</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - M-DWGs_Bid Set.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>M500</t>
+  </si>
+  <si>
+    <t>Mechanical Schedules</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: EF-1 added; RTU-1 to RTU-4 performance revised (RTU-1 MOP 50 to 60A); CRG-3 revised, TG-1 added</t>
+  </si>
+  <si>
+    <t>M600</t>
+  </si>
+  <si>
+    <t>Mechanical Details</t>
+  </si>
+  <si>
+    <t>M601</t>
+  </si>
+  <si>
+    <t>M602</t>
+  </si>
+  <si>
+    <t>Mechanical - Bakery Hood Details</t>
+  </si>
+  <si>
+    <t>M901</t>
+  </si>
+  <si>
+    <t>Mechanical Comcheck</t>
+  </si>
+  <si>
+    <t>M902</t>
+  </si>
+  <si>
+    <t>P000</t>
+  </si>
+  <si>
+    <t>General Plumbing Information</t>
+  </si>
+  <si>
+    <t>Plumbing</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - P-DWGs_Bid Set.pdf; P-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>Underground - Plumbing Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: GI moved ~8.8' W; 4" GW -8.6 LF, -1 FCO; sanitary exit moved ~9' W</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - P-DWGs_Bid Set.pdf; P-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>Plumbing Plan</t>
+  </si>
+  <si>
+    <t>P102</t>
+  </si>
+  <si>
+    <t>Enlarged Plumbing Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: GI/sanitary re-route; GI vent moved to IT Room 112</t>
+  </si>
+  <si>
+    <t>P500</t>
+  </si>
+  <si>
+    <t>Plumbing Schedules</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: SK-3 single faucet, new sink model; EWH-1 (50 gal, 6 kW, 480V) added to schedule</t>
+  </si>
+  <si>
+    <t>P600</t>
+  </si>
+  <si>
+    <t>Plumbing Details</t>
+  </si>
+  <si>
+    <t>FP000</t>
+  </si>
+  <si>
+    <t>General Fire Protection Information</t>
+  </si>
+  <si>
+    <t>Fire Protection</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - FP-DWGs_Bid Set.pdf; FP-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>FP101</t>
+  </si>
+  <si>
+    <t>Fire Protection Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: FDC added; Sales area 14,961 to 15,095 SF (not clouded)</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - FP-DWGs_Bid Set.pdf; FP-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>FP600</t>
+  </si>
+  <si>
+    <t>Fire Protection Details</t>
+  </si>
+  <si>
+    <t>E000</t>
+  </si>
+  <si>
+    <t>Symbols List and General Notes - Electrical</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>Electrical Site Plan</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Permit Cycle 2 (not in Bid Set; no narrative)</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): sign circuits 2-pole to 1-pole</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - E-DWGs_Bid Set.pdf; E-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf; E-DWGs_CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>E102</t>
+  </si>
+  <si>
+    <t>Ground Floor - Cable Wireway Plan</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Permit Cycle 2 (not in Bid Set; no narrative): background updated for fixture plan; cable tray unchanged</t>
+  </si>
+  <si>
+    <t>E103</t>
+  </si>
+  <si>
+    <t>Roof - Electrical Plan</t>
+  </si>
+  <si>
+    <t>E200</t>
+  </si>
+  <si>
+    <t>Comcheck - Electrical</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: COMcheck interior lighting 14,055 W to 15,191 W</t>
+  </si>
+  <si>
+    <t>E201</t>
+  </si>
+  <si>
+    <t>Ground Floor - Lighting Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: sales lighting re-layout (DF2-6 54 to 86, DF2-8 115 to 84, DF2-4 24 to 8, SK2 38 to 65)</t>
+  </si>
+  <si>
+    <t>E202</t>
+  </si>
+  <si>
+    <t>Lighting Controls and Schedules</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: luminaire schedule wattages deleted (not clouded)</t>
+  </si>
+  <si>
+    <t>E203</t>
+  </si>
+  <si>
+    <t>Electrical - Lighting Contactor Detail</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: lighting contactor circuits reassigned (no poles added)</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: bakery background shift; BK1-9 receptacle symbol missing (not clouded)</t>
+  </si>
+  <si>
+    <t>E400</t>
+  </si>
+  <si>
+    <t>Electrical Riser Diagrams</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: RTU-1 feeder 50A to 60A, 4#4 + #10G in 1-1/4" C (not clouded)</t>
+  </si>
+  <si>
+    <t>E401</t>
+  </si>
+  <si>
+    <t>Electrical - Metering Detail</t>
+  </si>
+  <si>
+    <t>E500</t>
+  </si>
+  <si>
+    <t>Electrical Schedules - Powered Equipment</t>
+  </si>
+  <si>
+    <t>E600</t>
+  </si>
+  <si>
+    <t>Electrical Details</t>
+  </si>
+  <si>
+    <t>E601</t>
+  </si>
+  <si>
+    <t>E602</t>
+  </si>
+  <si>
+    <t>Electrical - Pathway Details</t>
+  </si>
+  <si>
+    <t>E603</t>
+  </si>
+  <si>
+    <t>E604</t>
+  </si>
+  <si>
+    <t>E605</t>
+  </si>
+  <si>
+    <t>E606</t>
+  </si>
+  <si>
+    <t>Electrical - Bakery Hood Details</t>
+  </si>
+  <si>
+    <t>E607</t>
+  </si>
+  <si>
+    <t>Door Details - Electrical</t>
+  </si>
+  <si>
+    <t>FA101</t>
+  </si>
+  <si>
+    <t>Ground Floor - Fire Alarm Plan</t>
+  </si>
+  <si>
+    <t>Fire Alarm</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Permit Cycle 2 (not in Bid Set; no narrative): background updated; no device changes</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - FA-DWGs_Bid Set.pdf; FA-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>FA102</t>
+  </si>
+  <si>
+    <t>Fire Alarm Graphic Panel</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Permit Cycle 2 (not in Bid Set; no narrative): graphic annunciator background updated; no device changes</t>
+  </si>
+  <si>
+    <t>T000</t>
+  </si>
+  <si>
+    <t>Symbols List and General Notes - Technology</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - T-DWGs_Bid Set.pdf; T-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - T-DWGs_Bid Set.pdf; T-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf; T101-CCD2.pdf; CCD2_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>T201</t>
+  </si>
+  <si>
+    <t>Ground Floor - Security Plan</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: checkout cameras/PVM moved; CA01-08 to panoramic CA03-34; +1 door contact; new keynotes 1-8 (not clouded)</t>
+  </si>
+  <si>
+    <t>T300</t>
+  </si>
+  <si>
+    <t>Enlarged Technology Plans</t>
+  </si>
+  <si>
+    <t>T600</t>
+  </si>
+  <si>
+    <t>Technology Details</t>
+  </si>
+  <si>
+    <t>2025-12-18 — Permit Cycle 2 (not in Bid Set; no narrative): camera schedule CA09/CA10/PVM furnish/install cells blanked</t>
+  </si>
+  <si>
+    <t>T601</t>
+  </si>
+  <si>
+    <t>Hussmann R4.1 EMS RS485 Wiring</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Not reissued in CCD 01 set; duplicates R set (still on G101 index)</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - T-DWGs_Bid Set.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>T602</t>
+  </si>
+  <si>
+    <t>Hussmann R4.2 EMS Ethernet Wiring</t>
+  </si>
+  <si>
+    <t>BMS-000</t>
+  </si>
+  <si>
+    <t>BMS Symbols, Notes &amp; Abbreviations</t>
+  </si>
+  <si>
+    <t>BMS</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - BMS-DWGs_Bid Set.pdf; BMS-DWGs_CCD1.pdf</t>
+  </si>
+  <si>
+    <t>BMS-101</t>
+  </si>
+  <si>
+    <t>BMS Floor Plan</t>
+  </si>
+  <si>
+    <t>2026-01-14 — Permit Cycle 3 (not in Bid Set; no narrative): gas meter Modbus relocated</t>
+  </si>
+  <si>
+    <t>2026-05-28 — CCD 01: RTU-2 temp/RH sensors moved to new power pole</t>
+  </si>
+  <si>
+    <t>Lidl 1517 - BMS-DWGs_Bid Set.pdf; BMS-DWGs_CCD1.pdf; CCD1_Comparison_QTO.pdf</t>
+  </si>
+  <si>
+    <t>BMS-102</t>
+  </si>
+  <si>
+    <t>BMS Roof Plan</t>
+  </si>
+  <si>
+    <t>BMS-401</t>
+  </si>
+  <si>
+    <t>BMS Network Layout</t>
+  </si>
+  <si>
+    <t>BMS-402</t>
+  </si>
+  <si>
+    <t>Rtu-1 Control Details</t>
+  </si>
+  <si>
+    <t>BMS-403</t>
+  </si>
+  <si>
+    <t>Rtu-2,3,4 Control Details</t>
+  </si>
+  <si>
+    <t>BMS-404</t>
+  </si>
+  <si>
+    <t>Exhaust Fans &amp; AC Unit Controls</t>
+  </si>
+  <si>
+    <t>2026-05-28 — Reissued in CCD 01 set, no revision entry: DSF list 1..8 corrected to 1..10 (not clouded)</t>
+  </si>
+  <si>
+    <t>BMS-405</t>
+  </si>
+  <si>
+    <t>Input/Out Point Controls</t>
+  </si>
+  <si>
+    <t>BMS-406</t>
+  </si>
+  <si>
+    <t>Control Details</t>
   </si>
 </sst>
 </file>
@@ -17428,203 +18319,3519 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="C5" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D5" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="E5" t="s">
-        <v>584</v>
-      </c>
-      <c r="F5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G5" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" s="25">
-        <v>46233</v>
+        <v>46036</v>
       </c>
       <c r="L5" t="s">
         <v>587</v>
       </c>
       <c r="M5" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="B6" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="C6" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D6" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="E6" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" s="25">
-        <v>46233</v>
+        <v>46036</v>
       </c>
       <c r="L6" t="s">
         <v>587</v>
       </c>
       <c r="M6" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="B7" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="C7" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D7" t="s">
-        <v>583</v>
-      </c>
-      <c r="E7" t="s">
-        <v>584</v>
-      </c>
-      <c r="F7" t="s">
-        <v>595</v>
-      </c>
-      <c r="G7" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="25">
-        <v>46233</v>
+        <v>46008</v>
       </c>
       <c r="L7" t="s">
         <v>587</v>
       </c>
       <c r="M7" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>597</v>
+        <v>619</v>
       </c>
       <c r="B8" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="C8" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D8" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="E8" t="s">
-        <v>599</v>
-      </c>
-      <c r="F8" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="25">
-        <v>46233</v>
+        <v>46170</v>
       </c>
       <c r="L8" t="s">
         <v>587</v>
       </c>
       <c r="M8" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="B9" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="C9" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D9" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="E9" t="s">
         <v>584</v>
       </c>
       <c r="F9" t="s">
-        <v>602</v>
-      </c>
-      <c r="G9" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="25">
-        <v>46233</v>
+        <v>46170</v>
       </c>
       <c r="L9" t="s">
         <v>587</v>
       </c>
       <c r="M9" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="B10" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="C10" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D10" t="s">
-        <v>583</v>
-      </c>
-      <c r="E10" t="s">
-        <v>584</v>
-      </c>
-      <c r="F10" t="s">
-        <v>607</v>
-      </c>
-      <c r="G10" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="25">
-        <v>46233</v>
+        <v>45968</v>
       </c>
       <c r="L10" t="s">
         <v>587</v>
       </c>
       <c r="M10" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>628</v>
+      </c>
+      <c r="B11" t="s">
+        <v>629</v>
+      </c>
+      <c r="C11" t="s">
         <v>609</v>
+      </c>
+      <c r="D11" t="s">
+        <v>627</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L11" t="s">
+        <v>587</v>
+      </c>
+      <c r="M11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B12" t="s">
+        <v>631</v>
+      </c>
+      <c r="C12" t="s">
+        <v>609</v>
+      </c>
+      <c r="D12" t="s">
+        <v>627</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L12" t="s">
+        <v>587</v>
+      </c>
+      <c r="M12" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>632</v>
+      </c>
+      <c r="B13" t="s">
+        <v>633</v>
+      </c>
+      <c r="C13" t="s">
+        <v>609</v>
+      </c>
+      <c r="D13" t="s">
+        <v>610</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="25">
+        <v>46008</v>
+      </c>
+      <c r="L13" t="s">
+        <v>587</v>
+      </c>
+      <c r="M13" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>634</v>
+      </c>
+      <c r="B14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C14" t="s">
+        <v>609</v>
+      </c>
+      <c r="D14" t="s">
+        <v>627</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L14" t="s">
+        <v>587</v>
+      </c>
+      <c r="M14" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>636</v>
+      </c>
+      <c r="B15" t="s">
+        <v>637</v>
+      </c>
+      <c r="C15" t="s">
+        <v>638</v>
+      </c>
+      <c r="D15" t="s">
+        <v>627</v>
+      </c>
+      <c r="E15" t="s">
+        <v>584</v>
+      </c>
+      <c r="F15" t="s">
+        <v>639</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L15" t="s">
+        <v>587</v>
+      </c>
+      <c r="M15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>641</v>
+      </c>
+      <c r="B16" t="s">
+        <v>642</v>
+      </c>
+      <c r="C16" t="s">
+        <v>638</v>
+      </c>
+      <c r="D16" t="s">
+        <v>627</v>
+      </c>
+      <c r="E16" t="s">
+        <v>584</v>
+      </c>
+      <c r="F16" t="s">
+        <v>643</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L16" t="s">
+        <v>587</v>
+      </c>
+      <c r="M16" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>644</v>
+      </c>
+      <c r="B17" t="s">
+        <v>645</v>
+      </c>
+      <c r="C17" t="s">
+        <v>638</v>
+      </c>
+      <c r="D17" t="s">
+        <v>610</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25">
+        <v>46008</v>
+      </c>
+      <c r="L17" t="s">
+        <v>587</v>
+      </c>
+      <c r="M17" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>647</v>
+      </c>
+      <c r="B18" t="s">
+        <v>648</v>
+      </c>
+      <c r="C18" t="s">
+        <v>638</v>
+      </c>
+      <c r="D18" t="s">
+        <v>610</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="25">
+        <v>46008</v>
+      </c>
+      <c r="L18" t="s">
+        <v>587</v>
+      </c>
+      <c r="M18" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>649</v>
+      </c>
+      <c r="B19" t="s">
+        <v>650</v>
+      </c>
+      <c r="C19" t="s">
+        <v>638</v>
+      </c>
+      <c r="D19" t="s">
+        <v>610</v>
+      </c>
+      <c r="E19" t="s">
+        <v>584</v>
+      </c>
+      <c r="F19" t="s">
+        <v>651</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L19" t="s">
+        <v>587</v>
+      </c>
+      <c r="M19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>652</v>
+      </c>
+      <c r="B20" t="s">
+        <v>653</v>
+      </c>
+      <c r="C20" t="s">
+        <v>638</v>
+      </c>
+      <c r="D20" t="s">
+        <v>610</v>
+      </c>
+      <c r="E20" t="s">
+        <v>654</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L20" t="s">
+        <v>587</v>
+      </c>
+      <c r="M20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>655</v>
+      </c>
+      <c r="B21" t="s">
+        <v>656</v>
+      </c>
+      <c r="C21" t="s">
+        <v>638</v>
+      </c>
+      <c r="D21" t="s">
+        <v>627</v>
+      </c>
+      <c r="E21" t="s">
+        <v>657</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L21" t="s">
+        <v>587</v>
+      </c>
+      <c r="M21" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>658</v>
+      </c>
+      <c r="B22" t="s">
+        <v>656</v>
+      </c>
+      <c r="C22" t="s">
+        <v>638</v>
+      </c>
+      <c r="D22" t="s">
+        <v>627</v>
+      </c>
+      <c r="E22" t="s">
+        <v>659</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L22" t="s">
+        <v>587</v>
+      </c>
+      <c r="M22" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>660</v>
+      </c>
+      <c r="B23" t="s">
+        <v>661</v>
+      </c>
+      <c r="C23" t="s">
+        <v>638</v>
+      </c>
+      <c r="D23" t="s">
+        <v>627</v>
+      </c>
+      <c r="E23" t="s">
+        <v>662</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L23" t="s">
+        <v>587</v>
+      </c>
+      <c r="M23" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>663</v>
+      </c>
+      <c r="B24" t="s">
+        <v>661</v>
+      </c>
+      <c r="C24" t="s">
+        <v>638</v>
+      </c>
+      <c r="D24" t="s">
+        <v>627</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L24" t="s">
+        <v>587</v>
+      </c>
+      <c r="M24" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>664</v>
+      </c>
+      <c r="B25" t="s">
+        <v>661</v>
+      </c>
+      <c r="C25" t="s">
+        <v>638</v>
+      </c>
+      <c r="D25" t="s">
+        <v>627</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L25" t="s">
+        <v>587</v>
+      </c>
+      <c r="M25" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>665</v>
+      </c>
+      <c r="B26" t="s">
+        <v>661</v>
+      </c>
+      <c r="C26" t="s">
+        <v>638</v>
+      </c>
+      <c r="D26" t="s">
+        <v>627</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L26" t="s">
+        <v>587</v>
+      </c>
+      <c r="M26" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>666</v>
+      </c>
+      <c r="B27" t="s">
+        <v>661</v>
+      </c>
+      <c r="C27" t="s">
+        <v>638</v>
+      </c>
+      <c r="D27" t="s">
+        <v>627</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L27" t="s">
+        <v>587</v>
+      </c>
+      <c r="M27" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>667</v>
+      </c>
+      <c r="B28" t="s">
+        <v>668</v>
+      </c>
+      <c r="C28" t="s">
+        <v>638</v>
+      </c>
+      <c r="D28" t="s">
+        <v>610</v>
+      </c>
+      <c r="E28" t="s">
+        <v>669</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L28" t="s">
+        <v>587</v>
+      </c>
+      <c r="M28" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>670</v>
+      </c>
+      <c r="B29" t="s">
+        <v>668</v>
+      </c>
+      <c r="C29" t="s">
+        <v>638</v>
+      </c>
+      <c r="D29" t="s">
+        <v>610</v>
+      </c>
+      <c r="E29" t="s">
+        <v>671</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" s="25">
+        <v>46036</v>
+      </c>
+      <c r="L29" t="s">
+        <v>587</v>
+      </c>
+      <c r="M29" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>672</v>
+      </c>
+      <c r="B30" t="s">
+        <v>673</v>
+      </c>
+      <c r="C30" t="s">
+        <v>638</v>
+      </c>
+      <c r="D30" t="s">
+        <v>627</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L30" t="s">
+        <v>587</v>
+      </c>
+      <c r="M30" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>674</v>
+      </c>
+      <c r="B31" t="s">
+        <v>673</v>
+      </c>
+      <c r="C31" t="s">
+        <v>638</v>
+      </c>
+      <c r="D31" t="s">
+        <v>627</v>
+      </c>
+      <c r="E31" t="s">
+        <v>675</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L31" t="s">
+        <v>587</v>
+      </c>
+      <c r="M31" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>676</v>
+      </c>
+      <c r="B32" t="s">
+        <v>673</v>
+      </c>
+      <c r="C32" t="s">
+        <v>638</v>
+      </c>
+      <c r="D32" t="s">
+        <v>627</v>
+      </c>
+      <c r="E32" t="s">
+        <v>677</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L32" t="s">
+        <v>587</v>
+      </c>
+      <c r="M32" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>678</v>
+      </c>
+      <c r="B33" t="s">
+        <v>679</v>
+      </c>
+      <c r="C33" t="s">
+        <v>638</v>
+      </c>
+      <c r="D33" t="s">
+        <v>680</v>
+      </c>
+      <c r="E33" t="s">
+        <v>681</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="25">
+        <v>45908</v>
+      </c>
+      <c r="L33" t="s">
+        <v>682</v>
+      </c>
+      <c r="M33" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>684</v>
+      </c>
+      <c r="B34" t="s">
+        <v>685</v>
+      </c>
+      <c r="C34" t="s">
+        <v>638</v>
+      </c>
+      <c r="D34" t="s">
+        <v>610</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" s="25">
+        <v>46008</v>
+      </c>
+      <c r="L34" t="s">
+        <v>587</v>
+      </c>
+      <c r="M34" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>686</v>
+      </c>
+      <c r="B35" t="s">
+        <v>685</v>
+      </c>
+      <c r="C35" t="s">
+        <v>638</v>
+      </c>
+      <c r="D35" t="s">
+        <v>627</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L35" t="s">
+        <v>587</v>
+      </c>
+      <c r="M35" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>687</v>
+      </c>
+      <c r="B36" t="s">
+        <v>688</v>
+      </c>
+      <c r="C36" t="s">
+        <v>638</v>
+      </c>
+      <c r="D36" t="s">
+        <v>627</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L36" t="s">
+        <v>587</v>
+      </c>
+      <c r="M36" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>689</v>
+      </c>
+      <c r="B37" t="s">
+        <v>690</v>
+      </c>
+      <c r="C37" t="s">
+        <v>638</v>
+      </c>
+      <c r="D37" t="s">
+        <v>627</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L37" t="s">
+        <v>587</v>
+      </c>
+      <c r="M37" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>691</v>
+      </c>
+      <c r="B38" t="s">
+        <v>692</v>
+      </c>
+      <c r="C38" t="s">
+        <v>638</v>
+      </c>
+      <c r="D38" t="s">
+        <v>627</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L38" t="s">
+        <v>587</v>
+      </c>
+      <c r="M38" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>693</v>
+      </c>
+      <c r="B39" t="s">
+        <v>692</v>
+      </c>
+      <c r="C39" t="s">
+        <v>638</v>
+      </c>
+      <c r="D39" t="s">
+        <v>627</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L39" t="s">
+        <v>587</v>
+      </c>
+      <c r="M39" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>694</v>
+      </c>
+      <c r="B40" t="s">
+        <v>692</v>
+      </c>
+      <c r="C40" t="s">
+        <v>638</v>
+      </c>
+      <c r="D40" t="s">
+        <v>627</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L40" t="s">
+        <v>587</v>
+      </c>
+      <c r="M40" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>695</v>
+      </c>
+      <c r="B41" t="s">
+        <v>692</v>
+      </c>
+      <c r="C41" t="s">
+        <v>638</v>
+      </c>
+      <c r="D41" t="s">
+        <v>627</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L41" t="s">
+        <v>587</v>
+      </c>
+      <c r="M41" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>696</v>
+      </c>
+      <c r="B42" t="s">
+        <v>697</v>
+      </c>
+      <c r="C42" t="s">
+        <v>638</v>
+      </c>
+      <c r="D42" t="s">
+        <v>627</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L42" t="s">
+        <v>587</v>
+      </c>
+      <c r="M42" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>698</v>
+      </c>
+      <c r="B43" t="s">
+        <v>699</v>
+      </c>
+      <c r="C43" t="s">
+        <v>638</v>
+      </c>
+      <c r="D43" t="s">
+        <v>627</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L43" t="s">
+        <v>587</v>
+      </c>
+      <c r="M43" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>700</v>
+      </c>
+      <c r="B44" t="s">
+        <v>701</v>
+      </c>
+      <c r="C44" t="s">
+        <v>638</v>
+      </c>
+      <c r="D44" t="s">
+        <v>627</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L44" t="s">
+        <v>587</v>
+      </c>
+      <c r="M44" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>702</v>
+      </c>
+      <c r="B45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C45" t="s">
+        <v>638</v>
+      </c>
+      <c r="D45" t="s">
+        <v>627</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L45" t="s">
+        <v>587</v>
+      </c>
+      <c r="M45" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>703</v>
+      </c>
+      <c r="B46" t="s">
+        <v>704</v>
+      </c>
+      <c r="C46" t="s">
+        <v>638</v>
+      </c>
+      <c r="D46" t="s">
+        <v>627</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L46" t="s">
+        <v>587</v>
+      </c>
+      <c r="M46" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>705</v>
+      </c>
+      <c r="B47" t="s">
+        <v>706</v>
+      </c>
+      <c r="C47" t="s">
+        <v>638</v>
+      </c>
+      <c r="D47" t="s">
+        <v>627</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L47" t="s">
+        <v>587</v>
+      </c>
+      <c r="M47" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>707</v>
+      </c>
+      <c r="B48" t="s">
+        <v>708</v>
+      </c>
+      <c r="C48" t="s">
+        <v>638</v>
+      </c>
+      <c r="D48" t="s">
+        <v>627</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L48" t="s">
+        <v>587</v>
+      </c>
+      <c r="M48" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>709</v>
+      </c>
+      <c r="B49" t="s">
+        <v>710</v>
+      </c>
+      <c r="C49" t="s">
+        <v>638</v>
+      </c>
+      <c r="D49" t="s">
+        <v>627</v>
+      </c>
+      <c r="E49" t="s">
+        <v>711</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" s="25">
+        <v>46036</v>
+      </c>
+      <c r="L49" t="s">
+        <v>587</v>
+      </c>
+      <c r="M49" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>712</v>
+      </c>
+      <c r="B50" t="s">
+        <v>713</v>
+      </c>
+      <c r="C50" t="s">
+        <v>638</v>
+      </c>
+      <c r="D50" t="s">
+        <v>627</v>
+      </c>
+      <c r="E50" t="s">
+        <v>714</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L50" t="s">
+        <v>587</v>
+      </c>
+      <c r="M50" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>715</v>
+      </c>
+      <c r="B51" t="s">
+        <v>716</v>
+      </c>
+      <c r="C51" t="s">
+        <v>638</v>
+      </c>
+      <c r="D51" t="s">
+        <v>627</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L51" t="s">
+        <v>587</v>
+      </c>
+      <c r="M51" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>717</v>
+      </c>
+      <c r="B52" t="s">
+        <v>718</v>
+      </c>
+      <c r="C52" t="s">
+        <v>638</v>
+      </c>
+      <c r="D52" t="s">
+        <v>627</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L52" t="s">
+        <v>587</v>
+      </c>
+      <c r="M52" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>719</v>
+      </c>
+      <c r="B53" t="s">
+        <v>720</v>
+      </c>
+      <c r="C53" t="s">
+        <v>638</v>
+      </c>
+      <c r="D53" t="s">
+        <v>627</v>
+      </c>
+      <c r="E53" t="s">
+        <v>584</v>
+      </c>
+      <c r="F53" t="s">
+        <v>721</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L53" t="s">
+        <v>587</v>
+      </c>
+      <c r="M53" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>722</v>
+      </c>
+      <c r="B54" t="s">
+        <v>723</v>
+      </c>
+      <c r="C54" t="s">
+        <v>638</v>
+      </c>
+      <c r="D54" t="s">
+        <v>627</v>
+      </c>
+      <c r="E54" t="s">
+        <v>584</v>
+      </c>
+      <c r="F54" t="s">
+        <v>724</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L54" t="s">
+        <v>587</v>
+      </c>
+      <c r="M54" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>725</v>
+      </c>
+      <c r="B55" t="s">
+        <v>726</v>
+      </c>
+      <c r="C55" t="s">
+        <v>638</v>
+      </c>
+      <c r="D55" t="s">
+        <v>627</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L55" t="s">
+        <v>587</v>
+      </c>
+      <c r="M55" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>727</v>
+      </c>
+      <c r="B56" t="s">
+        <v>614</v>
+      </c>
+      <c r="C56" t="s">
+        <v>728</v>
+      </c>
+      <c r="D56" t="s">
+        <v>583</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L56" t="s">
+        <v>587</v>
+      </c>
+      <c r="M56" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>730</v>
+      </c>
+      <c r="B57" t="s">
+        <v>731</v>
+      </c>
+      <c r="C57" t="s">
+        <v>728</v>
+      </c>
+      <c r="D57" t="s">
+        <v>627</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L57" t="s">
+        <v>587</v>
+      </c>
+      <c r="M57" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>732</v>
+      </c>
+      <c r="B58" t="s">
+        <v>733</v>
+      </c>
+      <c r="C58" t="s">
+        <v>728</v>
+      </c>
+      <c r="D58" t="s">
+        <v>583</v>
+      </c>
+      <c r="E58" t="s">
+        <v>734</v>
+      </c>
+      <c r="F58" t="s">
+        <v>735</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L58" t="s">
+        <v>587</v>
+      </c>
+      <c r="M58" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>737</v>
+      </c>
+      <c r="B59" t="s">
+        <v>738</v>
+      </c>
+      <c r="C59" t="s">
+        <v>728</v>
+      </c>
+      <c r="D59" t="s">
+        <v>583</v>
+      </c>
+      <c r="E59" t="s">
+        <v>739</v>
+      </c>
+      <c r="F59" t="s">
+        <v>740</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L59" t="s">
+        <v>587</v>
+      </c>
+      <c r="M59" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>741</v>
+      </c>
+      <c r="B60" t="s">
+        <v>742</v>
+      </c>
+      <c r="C60" t="s">
+        <v>728</v>
+      </c>
+      <c r="D60" t="s">
+        <v>627</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L60" t="s">
+        <v>587</v>
+      </c>
+      <c r="M60" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>743</v>
+      </c>
+      <c r="B61" t="s">
+        <v>744</v>
+      </c>
+      <c r="C61" t="s">
+        <v>728</v>
+      </c>
+      <c r="D61" t="s">
+        <v>583</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L61" t="s">
+        <v>587</v>
+      </c>
+      <c r="M61" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>745</v>
+      </c>
+      <c r="B62" t="s">
+        <v>744</v>
+      </c>
+      <c r="C62" t="s">
+        <v>728</v>
+      </c>
+      <c r="D62" t="s">
+        <v>583</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L62" t="s">
+        <v>587</v>
+      </c>
+      <c r="M62" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>746</v>
+      </c>
+      <c r="B63" t="s">
+        <v>747</v>
+      </c>
+      <c r="C63" t="s">
+        <v>728</v>
+      </c>
+      <c r="D63" t="s">
+        <v>583</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L63" t="s">
+        <v>587</v>
+      </c>
+      <c r="M63" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>748</v>
+      </c>
+      <c r="B64" t="s">
+        <v>749</v>
+      </c>
+      <c r="C64" t="s">
+        <v>728</v>
+      </c>
+      <c r="D64" t="s">
+        <v>583</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L64" t="s">
+        <v>587</v>
+      </c>
+      <c r="M64" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>750</v>
+      </c>
+      <c r="B65" t="s">
+        <v>749</v>
+      </c>
+      <c r="C65" t="s">
+        <v>728</v>
+      </c>
+      <c r="D65" t="s">
+        <v>583</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L65" t="s">
+        <v>587</v>
+      </c>
+      <c r="M65" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>751</v>
+      </c>
+      <c r="B66" t="s">
+        <v>749</v>
+      </c>
+      <c r="C66" t="s">
+        <v>728</v>
+      </c>
+      <c r="D66" t="s">
+        <v>583</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L66" t="s">
+        <v>587</v>
+      </c>
+      <c r="M66" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>752</v>
+      </c>
+      <c r="B67" t="s">
+        <v>749</v>
+      </c>
+      <c r="C67" t="s">
+        <v>728</v>
+      </c>
+      <c r="D67" t="s">
+        <v>627</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L67" t="s">
+        <v>587</v>
+      </c>
+      <c r="M67" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>753</v>
+      </c>
+      <c r="B68" t="s">
+        <v>754</v>
+      </c>
+      <c r="C68" t="s">
+        <v>755</v>
+      </c>
+      <c r="D68" t="s">
+        <v>627</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L68" t="s">
+        <v>587</v>
+      </c>
+      <c r="M68" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>757</v>
+      </c>
+      <c r="B69" t="s">
+        <v>758</v>
+      </c>
+      <c r="C69" t="s">
+        <v>755</v>
+      </c>
+      <c r="D69" t="s">
+        <v>583</v>
+      </c>
+      <c r="E69" t="s">
+        <v>759</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L69" t="s">
+        <v>587</v>
+      </c>
+      <c r="M69" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>761</v>
+      </c>
+      <c r="B70" t="s">
+        <v>762</v>
+      </c>
+      <c r="C70" t="s">
+        <v>755</v>
+      </c>
+      <c r="D70" t="s">
+        <v>627</v>
+      </c>
+      <c r="E70" t="s">
+        <v>763</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L70" t="s">
+        <v>587</v>
+      </c>
+      <c r="M70" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>764</v>
+      </c>
+      <c r="B71" t="s">
+        <v>765</v>
+      </c>
+      <c r="C71" t="s">
+        <v>755</v>
+      </c>
+      <c r="D71" t="s">
+        <v>583</v>
+      </c>
+      <c r="E71" t="s">
+        <v>766</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L71" t="s">
+        <v>587</v>
+      </c>
+      <c r="M71" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>767</v>
+      </c>
+      <c r="B72" t="s">
+        <v>768</v>
+      </c>
+      <c r="C72" t="s">
+        <v>755</v>
+      </c>
+      <c r="D72" t="s">
+        <v>769</v>
+      </c>
+      <c r="E72" t="s">
+        <v>770</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L72" t="s">
+        <v>682</v>
+      </c>
+      <c r="M72" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>772</v>
+      </c>
+      <c r="B73" t="s">
+        <v>773</v>
+      </c>
+      <c r="C73" t="s">
+        <v>755</v>
+      </c>
+      <c r="D73" t="s">
+        <v>627</v>
+      </c>
+      <c r="E73" t="s">
+        <v>774</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L73" t="s">
+        <v>587</v>
+      </c>
+      <c r="M73" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>775</v>
+      </c>
+      <c r="B74" t="s">
+        <v>776</v>
+      </c>
+      <c r="C74" t="s">
+        <v>755</v>
+      </c>
+      <c r="D74" t="s">
+        <v>627</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L74" t="s">
+        <v>587</v>
+      </c>
+      <c r="M74" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>777</v>
+      </c>
+      <c r="B75" t="s">
+        <v>776</v>
+      </c>
+      <c r="C75" t="s">
+        <v>755</v>
+      </c>
+      <c r="D75" t="s">
+        <v>627</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L75" t="s">
+        <v>587</v>
+      </c>
+      <c r="M75" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>778</v>
+      </c>
+      <c r="B76" t="s">
+        <v>779</v>
+      </c>
+      <c r="C76" t="s">
+        <v>755</v>
+      </c>
+      <c r="D76" t="s">
+        <v>627</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L76" t="s">
+        <v>587</v>
+      </c>
+      <c r="M76" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>780</v>
+      </c>
+      <c r="B77" t="s">
+        <v>781</v>
+      </c>
+      <c r="C77" t="s">
+        <v>755</v>
+      </c>
+      <c r="D77" t="s">
+        <v>583</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L77" t="s">
+        <v>587</v>
+      </c>
+      <c r="M77" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>782</v>
+      </c>
+      <c r="B78" t="s">
+        <v>781</v>
+      </c>
+      <c r="C78" t="s">
+        <v>755</v>
+      </c>
+      <c r="D78" t="s">
+        <v>583</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L78" t="s">
+        <v>587</v>
+      </c>
+      <c r="M78" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>783</v>
+      </c>
+      <c r="B79" t="s">
+        <v>784</v>
+      </c>
+      <c r="C79" t="s">
+        <v>785</v>
+      </c>
+      <c r="D79" t="s">
+        <v>627</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L79" t="s">
+        <v>587</v>
+      </c>
+      <c r="M79" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>787</v>
+      </c>
+      <c r="B80" t="s">
+        <v>788</v>
+      </c>
+      <c r="C80" t="s">
+        <v>785</v>
+      </c>
+      <c r="D80" t="s">
+        <v>583</v>
+      </c>
+      <c r="E80" t="s">
+        <v>789</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L80" t="s">
+        <v>587</v>
+      </c>
+      <c r="M80" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>791</v>
+      </c>
+      <c r="B81" t="s">
+        <v>792</v>
+      </c>
+      <c r="C81" t="s">
+        <v>785</v>
+      </c>
+      <c r="D81" t="s">
+        <v>627</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L81" t="s">
+        <v>587</v>
+      </c>
+      <c r="M81" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>793</v>
+      </c>
+      <c r="B82" t="s">
+        <v>794</v>
+      </c>
+      <c r="C82" t="s">
+        <v>785</v>
+      </c>
+      <c r="D82" t="s">
+        <v>583</v>
+      </c>
+      <c r="E82" t="s">
+        <v>795</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L82" t="s">
+        <v>587</v>
+      </c>
+      <c r="M82" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>796</v>
+      </c>
+      <c r="B83" t="s">
+        <v>797</v>
+      </c>
+      <c r="C83" t="s">
+        <v>785</v>
+      </c>
+      <c r="D83" t="s">
+        <v>583</v>
+      </c>
+      <c r="E83" t="s">
+        <v>584</v>
+      </c>
+      <c r="F83" t="s">
+        <v>798</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L83" t="s">
+        <v>587</v>
+      </c>
+      <c r="M83" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>799</v>
+      </c>
+      <c r="B84" t="s">
+        <v>800</v>
+      </c>
+      <c r="C84" t="s">
+        <v>785</v>
+      </c>
+      <c r="D84" t="s">
+        <v>583</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L84" t="s">
+        <v>587</v>
+      </c>
+      <c r="M84" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>801</v>
+      </c>
+      <c r="B85" t="s">
+        <v>802</v>
+      </c>
+      <c r="C85" t="s">
+        <v>803</v>
+      </c>
+      <c r="D85" t="s">
+        <v>627</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L85" t="s">
+        <v>587</v>
+      </c>
+      <c r="M85" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>805</v>
+      </c>
+      <c r="B86" t="s">
+        <v>806</v>
+      </c>
+      <c r="C86" t="s">
+        <v>803</v>
+      </c>
+      <c r="D86" t="s">
+        <v>627</v>
+      </c>
+      <c r="E86" t="s">
+        <v>807</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L86" t="s">
+        <v>587</v>
+      </c>
+      <c r="M86" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>809</v>
+      </c>
+      <c r="B87" t="s">
+        <v>810</v>
+      </c>
+      <c r="C87" t="s">
+        <v>803</v>
+      </c>
+      <c r="D87" t="s">
+        <v>627</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L87" t="s">
+        <v>587</v>
+      </c>
+      <c r="M87" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>811</v>
+      </c>
+      <c r="B88" t="s">
+        <v>812</v>
+      </c>
+      <c r="C88" t="s">
+        <v>582</v>
+      </c>
+      <c r="D88" t="s">
+        <v>583</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L88" t="s">
+        <v>587</v>
+      </c>
+      <c r="M88" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>814</v>
+      </c>
+      <c r="B89" t="s">
+        <v>815</v>
+      </c>
+      <c r="C89" t="s">
+        <v>582</v>
+      </c>
+      <c r="D89" t="s">
+        <v>627</v>
+      </c>
+      <c r="E89" t="s">
+        <v>816</v>
+      </c>
+      <c r="F89" t="s">
+        <v>817</v>
+      </c>
+      <c r="J89">
+        <v>2</v>
+      </c>
+      <c r="K89" s="25">
+        <v>46036</v>
+      </c>
+      <c r="L89" t="s">
+        <v>587</v>
+      </c>
+      <c r="M89" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>580</v>
+      </c>
+      <c r="B90" t="s">
+        <v>581</v>
+      </c>
+      <c r="C90" t="s">
+        <v>582</v>
+      </c>
+      <c r="D90" t="s">
+        <v>583</v>
+      </c>
+      <c r="E90" t="s">
+        <v>584</v>
+      </c>
+      <c r="F90" t="s">
+        <v>585</v>
+      </c>
+      <c r="G90" t="s">
+        <v>586</v>
+      </c>
+      <c r="J90">
+        <v>3</v>
+      </c>
+      <c r="K90" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L90" t="s">
+        <v>587</v>
+      </c>
+      <c r="M90" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>820</v>
+      </c>
+      <c r="B91" t="s">
+        <v>821</v>
+      </c>
+      <c r="C91" t="s">
+        <v>582</v>
+      </c>
+      <c r="D91" t="s">
+        <v>627</v>
+      </c>
+      <c r="E91" t="s">
+        <v>822</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L91" t="s">
+        <v>587</v>
+      </c>
+      <c r="M91" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>823</v>
+      </c>
+      <c r="B92" t="s">
+        <v>824</v>
+      </c>
+      <c r="C92" t="s">
+        <v>582</v>
+      </c>
+      <c r="D92" t="s">
+        <v>583</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L92" t="s">
+        <v>587</v>
+      </c>
+      <c r="M92" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>825</v>
+      </c>
+      <c r="B93" t="s">
+        <v>826</v>
+      </c>
+      <c r="C93" t="s">
+        <v>582</v>
+      </c>
+      <c r="D93" t="s">
+        <v>583</v>
+      </c>
+      <c r="E93" t="s">
+        <v>827</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L93" t="s">
+        <v>587</v>
+      </c>
+      <c r="M93" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>828</v>
+      </c>
+      <c r="B94" t="s">
+        <v>829</v>
+      </c>
+      <c r="C94" t="s">
+        <v>582</v>
+      </c>
+      <c r="D94" t="s">
+        <v>583</v>
+      </c>
+      <c r="E94" t="s">
+        <v>584</v>
+      </c>
+      <c r="F94" t="s">
+        <v>830</v>
+      </c>
+      <c r="J94">
+        <v>2</v>
+      </c>
+      <c r="K94" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L94" t="s">
+        <v>587</v>
+      </c>
+      <c r="M94" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>831</v>
+      </c>
+      <c r="B95" t="s">
+        <v>832</v>
+      </c>
+      <c r="C95" t="s">
+        <v>582</v>
+      </c>
+      <c r="D95" t="s">
+        <v>583</v>
+      </c>
+      <c r="E95" t="s">
+        <v>833</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L95" t="s">
+        <v>587</v>
+      </c>
+      <c r="M95" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>834</v>
+      </c>
+      <c r="B96" t="s">
+        <v>835</v>
+      </c>
+      <c r="C96" t="s">
+        <v>582</v>
+      </c>
+      <c r="D96" t="s">
+        <v>627</v>
+      </c>
+      <c r="E96" t="s">
+        <v>816</v>
+      </c>
+      <c r="F96" t="s">
+        <v>584</v>
+      </c>
+      <c r="G96" t="s">
+        <v>836</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+      <c r="K96" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L96" t="s">
+        <v>587</v>
+      </c>
+      <c r="M96" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>588</v>
+      </c>
+      <c r="B97" t="s">
+        <v>589</v>
+      </c>
+      <c r="C97" t="s">
+        <v>582</v>
+      </c>
+      <c r="D97" t="s">
+        <v>583</v>
+      </c>
+      <c r="E97" t="s">
+        <v>837</v>
+      </c>
+      <c r="F97" t="s">
+        <v>590</v>
+      </c>
+      <c r="J97">
+        <v>2</v>
+      </c>
+      <c r="K97" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L97" t="s">
+        <v>587</v>
+      </c>
+      <c r="M97" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>591</v>
+      </c>
+      <c r="B98" t="s">
+        <v>592</v>
+      </c>
+      <c r="C98" t="s">
+        <v>582</v>
+      </c>
+      <c r="D98" t="s">
+        <v>583</v>
+      </c>
+      <c r="E98" t="s">
+        <v>584</v>
+      </c>
+      <c r="F98" t="s">
+        <v>593</v>
+      </c>
+      <c r="G98" t="s">
+        <v>594</v>
+      </c>
+      <c r="J98">
+        <v>3</v>
+      </c>
+      <c r="K98" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L98" t="s">
+        <v>587</v>
+      </c>
+      <c r="M98" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>838</v>
+      </c>
+      <c r="B99" t="s">
+        <v>839</v>
+      </c>
+      <c r="C99" t="s">
+        <v>582</v>
+      </c>
+      <c r="D99" t="s">
+        <v>583</v>
+      </c>
+      <c r="E99" t="s">
+        <v>840</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L99" t="s">
+        <v>587</v>
+      </c>
+      <c r="M99" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>841</v>
+      </c>
+      <c r="B100" t="s">
+        <v>842</v>
+      </c>
+      <c r="C100" t="s">
+        <v>582</v>
+      </c>
+      <c r="D100" t="s">
+        <v>627</v>
+      </c>
+      <c r="E100" t="s">
+        <v>816</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L100" t="s">
+        <v>587</v>
+      </c>
+      <c r="M100" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>843</v>
+      </c>
+      <c r="B101" t="s">
+        <v>844</v>
+      </c>
+      <c r="C101" t="s">
+        <v>582</v>
+      </c>
+      <c r="D101" t="s">
+        <v>627</v>
+      </c>
+      <c r="E101" t="s">
+        <v>816</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L101" t="s">
+        <v>587</v>
+      </c>
+      <c r="M101" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>595</v>
+      </c>
+      <c r="B102" t="s">
+        <v>596</v>
+      </c>
+      <c r="C102" t="s">
+        <v>582</v>
+      </c>
+      <c r="D102" t="s">
+        <v>583</v>
+      </c>
+      <c r="E102" t="s">
+        <v>597</v>
+      </c>
+      <c r="F102" t="s">
+        <v>598</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="K102" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L102" t="s">
+        <v>587</v>
+      </c>
+      <c r="M102" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>599</v>
+      </c>
+      <c r="B103" t="s">
+        <v>596</v>
+      </c>
+      <c r="C103" t="s">
+        <v>582</v>
+      </c>
+      <c r="D103" t="s">
+        <v>583</v>
+      </c>
+      <c r="E103" t="s">
+        <v>584</v>
+      </c>
+      <c r="F103" t="s">
+        <v>600</v>
+      </c>
+      <c r="G103" t="s">
+        <v>601</v>
+      </c>
+      <c r="J103">
+        <v>3</v>
+      </c>
+      <c r="K103" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L103" t="s">
+        <v>587</v>
+      </c>
+      <c r="M103" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>845</v>
+      </c>
+      <c r="B104" t="s">
+        <v>846</v>
+      </c>
+      <c r="C104" t="s">
+        <v>582</v>
+      </c>
+      <c r="D104" t="s">
+        <v>583</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L104" t="s">
+        <v>587</v>
+      </c>
+      <c r="M104" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>847</v>
+      </c>
+      <c r="B105" t="s">
+        <v>846</v>
+      </c>
+      <c r="C105" t="s">
+        <v>582</v>
+      </c>
+      <c r="D105" t="s">
+        <v>583</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L105" t="s">
+        <v>587</v>
+      </c>
+      <c r="M105" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>848</v>
+      </c>
+      <c r="B106" t="s">
+        <v>849</v>
+      </c>
+      <c r="C106" t="s">
+        <v>582</v>
+      </c>
+      <c r="D106" t="s">
+        <v>627</v>
+      </c>
+      <c r="E106" t="s">
+        <v>816</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L106" t="s">
+        <v>587</v>
+      </c>
+      <c r="M106" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>850</v>
+      </c>
+      <c r="B107" t="s">
+        <v>849</v>
+      </c>
+      <c r="C107" t="s">
+        <v>582</v>
+      </c>
+      <c r="D107" t="s">
+        <v>627</v>
+      </c>
+      <c r="E107" t="s">
+        <v>816</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L107" t="s">
+        <v>587</v>
+      </c>
+      <c r="M107" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>851</v>
+      </c>
+      <c r="B108" t="s">
+        <v>849</v>
+      </c>
+      <c r="C108" t="s">
+        <v>582</v>
+      </c>
+      <c r="D108" t="s">
+        <v>627</v>
+      </c>
+      <c r="E108" t="s">
+        <v>816</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L108" t="s">
+        <v>587</v>
+      </c>
+      <c r="M108" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>852</v>
+      </c>
+      <c r="B109" t="s">
+        <v>849</v>
+      </c>
+      <c r="C109" t="s">
+        <v>582</v>
+      </c>
+      <c r="D109" t="s">
+        <v>627</v>
+      </c>
+      <c r="E109" t="s">
+        <v>816</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L109" t="s">
+        <v>587</v>
+      </c>
+      <c r="M109" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>853</v>
+      </c>
+      <c r="B110" t="s">
+        <v>854</v>
+      </c>
+      <c r="C110" t="s">
+        <v>582</v>
+      </c>
+      <c r="D110" t="s">
+        <v>627</v>
+      </c>
+      <c r="E110" t="s">
+        <v>816</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L110" t="s">
+        <v>587</v>
+      </c>
+      <c r="M110" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>855</v>
+      </c>
+      <c r="B111" t="s">
+        <v>856</v>
+      </c>
+      <c r="C111" t="s">
+        <v>582</v>
+      </c>
+      <c r="D111" t="s">
+        <v>627</v>
+      </c>
+      <c r="E111" t="s">
+        <v>816</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L111" t="s">
+        <v>587</v>
+      </c>
+      <c r="M111" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>857</v>
+      </c>
+      <c r="B112" t="s">
+        <v>858</v>
+      </c>
+      <c r="C112" t="s">
+        <v>859</v>
+      </c>
+      <c r="D112" t="s">
+        <v>627</v>
+      </c>
+      <c r="E112" t="s">
+        <v>860</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L112" t="s">
+        <v>587</v>
+      </c>
+      <c r="M112" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>862</v>
+      </c>
+      <c r="B113" t="s">
+        <v>863</v>
+      </c>
+      <c r="C113" t="s">
+        <v>859</v>
+      </c>
+      <c r="D113" t="s">
+        <v>627</v>
+      </c>
+      <c r="E113" t="s">
+        <v>864</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L113" t="s">
+        <v>587</v>
+      </c>
+      <c r="M113" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>865</v>
+      </c>
+      <c r="B114" t="s">
+        <v>866</v>
+      </c>
+      <c r="C114" t="s">
+        <v>604</v>
+      </c>
+      <c r="D114" t="s">
+        <v>627</v>
+      </c>
+      <c r="E114" t="s">
+        <v>816</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L114" t="s">
+        <v>587</v>
+      </c>
+      <c r="M114" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>602</v>
+      </c>
+      <c r="B115" t="s">
+        <v>603</v>
+      </c>
+      <c r="C115" t="s">
+        <v>604</v>
+      </c>
+      <c r="D115" t="s">
+        <v>627</v>
+      </c>
+      <c r="E115" t="s">
+        <v>816</v>
+      </c>
+      <c r="F115" t="s">
+        <v>584</v>
+      </c>
+      <c r="G115" t="s">
+        <v>605</v>
+      </c>
+      <c r="H115" t="s">
+        <v>606</v>
+      </c>
+      <c r="J115">
+        <v>4</v>
+      </c>
+      <c r="K115" s="25">
+        <v>46233</v>
+      </c>
+      <c r="L115" t="s">
+        <v>587</v>
+      </c>
+      <c r="M115" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>869</v>
+      </c>
+      <c r="B116" t="s">
+        <v>870</v>
+      </c>
+      <c r="C116" t="s">
+        <v>604</v>
+      </c>
+      <c r="D116" t="s">
+        <v>627</v>
+      </c>
+      <c r="E116" t="s">
+        <v>816</v>
+      </c>
+      <c r="F116" t="s">
+        <v>584</v>
+      </c>
+      <c r="G116" t="s">
+        <v>871</v>
+      </c>
+      <c r="J116">
+        <v>3</v>
+      </c>
+      <c r="K116" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L116" t="s">
+        <v>587</v>
+      </c>
+      <c r="M116" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>872</v>
+      </c>
+      <c r="B117" t="s">
+        <v>873</v>
+      </c>
+      <c r="C117" t="s">
+        <v>604</v>
+      </c>
+      <c r="D117" t="s">
+        <v>627</v>
+      </c>
+      <c r="E117" t="s">
+        <v>816</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L117" t="s">
+        <v>587</v>
+      </c>
+      <c r="M117" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>874</v>
+      </c>
+      <c r="B118" t="s">
+        <v>875</v>
+      </c>
+      <c r="C118" t="s">
+        <v>604</v>
+      </c>
+      <c r="D118" t="s">
+        <v>627</v>
+      </c>
+      <c r="E118" t="s">
+        <v>876</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118" s="25">
+        <v>46009</v>
+      </c>
+      <c r="L118" t="s">
+        <v>587</v>
+      </c>
+      <c r="M118" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>877</v>
+      </c>
+      <c r="B119" t="s">
+        <v>878</v>
+      </c>
+      <c r="C119" t="s">
+        <v>604</v>
+      </c>
+      <c r="D119" t="s">
+        <v>769</v>
+      </c>
+      <c r="E119" t="s">
+        <v>879</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L119" t="s">
+        <v>682</v>
+      </c>
+      <c r="M119" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>881</v>
+      </c>
+      <c r="B120" t="s">
+        <v>882</v>
+      </c>
+      <c r="C120" t="s">
+        <v>604</v>
+      </c>
+      <c r="D120" t="s">
+        <v>769</v>
+      </c>
+      <c r="E120" t="s">
+        <v>879</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L120" t="s">
+        <v>682</v>
+      </c>
+      <c r="M120" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>883</v>
+      </c>
+      <c r="B121" t="s">
+        <v>884</v>
+      </c>
+      <c r="C121" t="s">
+        <v>885</v>
+      </c>
+      <c r="D121" t="s">
+        <v>627</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L121" t="s">
+        <v>587</v>
+      </c>
+      <c r="M121" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>887</v>
+      </c>
+      <c r="B122" t="s">
+        <v>888</v>
+      </c>
+      <c r="C122" t="s">
+        <v>885</v>
+      </c>
+      <c r="D122" t="s">
+        <v>627</v>
+      </c>
+      <c r="E122" t="s">
+        <v>889</v>
+      </c>
+      <c r="F122" t="s">
+        <v>890</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L122" t="s">
+        <v>587</v>
+      </c>
+      <c r="M122" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>892</v>
+      </c>
+      <c r="B123" t="s">
+        <v>893</v>
+      </c>
+      <c r="C123" t="s">
+        <v>885</v>
+      </c>
+      <c r="D123" t="s">
+        <v>627</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L123" t="s">
+        <v>587</v>
+      </c>
+      <c r="M123" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>894</v>
+      </c>
+      <c r="B124" t="s">
+        <v>895</v>
+      </c>
+      <c r="C124" t="s">
+        <v>885</v>
+      </c>
+      <c r="D124" t="s">
+        <v>627</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L124" t="s">
+        <v>587</v>
+      </c>
+      <c r="M124" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>896</v>
+      </c>
+      <c r="B125" t="s">
+        <v>897</v>
+      </c>
+      <c r="C125" t="s">
+        <v>885</v>
+      </c>
+      <c r="D125" t="s">
+        <v>627</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L125" t="s">
+        <v>587</v>
+      </c>
+      <c r="M125" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>898</v>
+      </c>
+      <c r="B126" t="s">
+        <v>899</v>
+      </c>
+      <c r="C126" t="s">
+        <v>885</v>
+      </c>
+      <c r="D126" t="s">
+        <v>627</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L126" t="s">
+        <v>587</v>
+      </c>
+      <c r="M126" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>900</v>
+      </c>
+      <c r="B127" t="s">
+        <v>901</v>
+      </c>
+      <c r="C127" t="s">
+        <v>885</v>
+      </c>
+      <c r="D127" t="s">
+        <v>627</v>
+      </c>
+      <c r="E127" t="s">
+        <v>902</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127" s="25">
+        <v>46170</v>
+      </c>
+      <c r="L127" t="s">
+        <v>587</v>
+      </c>
+      <c r="M127" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>903</v>
+      </c>
+      <c r="B128" t="s">
+        <v>904</v>
+      </c>
+      <c r="C128" t="s">
+        <v>885</v>
+      </c>
+      <c r="D128" t="s">
+        <v>627</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L128" t="s">
+        <v>587</v>
+      </c>
+      <c r="M128" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>905</v>
+      </c>
+      <c r="B129" t="s">
+        <v>906</v>
+      </c>
+      <c r="C129" t="s">
+        <v>885</v>
+      </c>
+      <c r="D129" t="s">
+        <v>627</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129" s="25">
+        <v>45968</v>
+      </c>
+      <c r="L129" t="s">
+        <v>587</v>
+      </c>
+      <c r="M129" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">

--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439FE3C-2054-4CF5-9257-E0CFDD99812F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99333E6-9D0A-43E6-83FE-FBBB719F976D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="17085" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="909">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1671,66 +1671,36 @@
     <t>33 4100</t>
   </si>
   <si>
-    <t>Stormwater Package Rev 0 (Procore 33 4100-2.0 / Fieldwire PSI-0002) - Hydro International First Defense hydrodynamic separator (ST8), Up-Flo water quality filter (ST5), Southeast Culvert 84in CMP underground detention. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/9; Procore has no due date.</t>
-  </si>
-  <si>
     <t>Coles Construction</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>SUB-002_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-002_Transmittal_Packaged.pdf (package INCLUDED, 62 pp) - folder: documents\submittals\SUB-002 - 334100 Storm Drainage</t>
-  </si>
-  <si>
     <t>SUB-003</t>
   </si>
   <si>
     <t>Coles Construction (supplier Core &amp; Main)</t>
   </si>
   <si>
-    <t>SUB-003_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-003_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-003 - 334100 Site Utilities</t>
-  </si>
-  <si>
-    <t>HDPE Pipe Rev 0 (Procore 33 4100-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - ADS N-12 ST IB storm pipe (pkg Section 1). Attachment is the full Core &amp; Main site utility package; Procore splits Package #1 into one item per spec section (sanitary = SUB-004). Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
-  </si>
-  <si>
     <t>SUB-004</t>
   </si>
   <si>
     <t>33 3000</t>
   </si>
   <si>
-    <t>Sanitary Sewer Rev 0 (Procore 33 3000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - Diamond Sani-21 PVC sewer pipe &amp; fittings, cleanouts, Star Pipe heavy-duty covers, marking tape (pkg Section 2, export pp. 8-19). Same PSI-0001 attachment as SUB-003. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
-  </si>
-  <si>
-    <t>SUB-004_R0_Original_Procore_Export_2026-10-01.pdf; SUB-004_R0_Sanitary_Section_Only.pdf; Submittal-004_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-004 - 333000 Sanitary Sewer</t>
-  </si>
-  <si>
     <t>SUB-005</t>
   </si>
   <si>
     <t>33 1000</t>
   </si>
   <si>
-    <t>Domestic Water &amp; Irrigation Rev 0 (Procore 33 1000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - PVC pressure pipe &amp; DI fittings, 2in tap assemblies (Smith-Blair 313, Ford Meter Box), 2in DCV (Wilkins 950XLT), irrigation, 2in RPZ (Wilkins 975XL2) (pkg Section 3, export pp. 20-53). Same PSI-0001 attachment as SUB-003/004. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11; Procore has no due date.</t>
-  </si>
-  <si>
-    <t>SUB-005_R0_Original_Procore_Export_2026-10-01.pdf; SUB-005_R0_Domestic_Water_Section_Only.pdf; Submittal-005_Transmittal_Packaged.pdf (package INCLUDED, 92 pp) - folder: documents\submittals\SUB-005 - 331000 Domestic Water</t>
-  </si>
-  <si>
     <t>SUB-006</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>Fire Main Rev 0 (Procore 33-1.0, Package #1 Site Utilities) - U.S. Pipe Tyton DI pipe &amp; fittings, tapping sleeve, M&amp;H 129 hydrant, 8in DCDA BFP vault (Wilkins 350ASTDA), 8in PIV, 8in gate valve (PSI-0001 pkg Section 4, export pp. 54-91). FLAG: Procore item has NO ATTACHMENT (cover only) and spec is division-level '33 - Utilities' - confirm CHA has the fire main cut sheets. Reviewer: CHA Consulting (Christopher Manes) - no response. Req'd return per Fieldwire response due 9/11.</t>
-  </si>
-  <si>
-    <t>SUB-006_R0_Procore_Cover_Only_2026-10-01.pdf (Procore item has NO attachment); SUB-006_R0_Fire_Main_Section_REFERENCE_from_PSI-0001.pdf (from SUB-003 copy); Submittal-006_Transmittal_Packaged.pdf (42 pp) - folder: documents\submittals\SUB-006 - 33 Fire Main</t>
-  </si>
-  <si>
     <t>SUB-007</t>
   </si>
   <si>
@@ -2821,6 +2791,42 @@
   </si>
   <si>
     <t>Control Details</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Stormwater Package Rev 0 (Procore 33 4100-2.0 / Fieldwire PSI-0002) - Hydro International First Defense separator (ST8), Up-Flo water quality filter (ST5), Southeast Culvert 84in CMP underground detention. CHA (Chris Manes) REJECTED 10/1/2026: items to be updated per revised site plan pending County review. ST8 no longer required; ST5 and CMP detention on hold pending revised civil plans. PSI response to Coles issued 10/5/2026 - resubmit as Rev 1 after revised civil plans issue.</t>
+  </si>
+  <si>
+    <t>SUB-002_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-002_Transmittal_Packaged.pdf; SUB-002_R0_CHA_Reviewed_Export_REJECTED_2026-10-05.pdf; SUB-002_R0_CHA_Reviewed_REJECTED_2026-10-01.pdf; SUB-002_R0_Response_to_Coles_REJECTED_2026-10-05.pdf (response + CHA review, 62 pp) - folder: documents\submittals\SUB-002 - 334100 Storm Drainage</t>
+  </si>
+  <si>
+    <t>Revise &amp; Resubmit</t>
+  </si>
+  <si>
+    <t>HDPE Pipe Rev 0 (Procore 33 4100-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - full Core &amp; Main site utility package. CHA (Chris Manes) REVISE &amp; RESUBMIT 10/1/2026 (one review for all Package #1 items): (1) sanitary sewer mains to be DIP (PVC Sani-21 submitted); (2) 3in water main to meet AWWA C900 (D2241 submitted); (3) irrigation tap/meter/BFP/main is 1in per approved plans - 2in submitted. No comments on storm HDPE or fire main. PSI response to Coles issued 10/5/2026 - resubmit full package as Rev 1.</t>
+  </si>
+  <si>
+    <t>SUB-003_R0_Original_Procore_Export_2026-10-01.pdf; Submittal-003_Transmittal_Packaged.pdf; SUB-003_R0_CHA_Reviewed_Export_R&amp;R_2026-10-05.pdf; SUB-003_R0_CHA_Reviewed_R&amp;R_2026-10-01.pdf; SUB-003_R0_Response_to_Coles_R&amp;R_2026-10-05.pdf (response + CHA review, 92 pp) - folder: documents\submittals\SUB-003 - 334100 Site Utilities</t>
+  </si>
+  <si>
+    <t>Sanitary Sewer Rev 0 (Procore 33 3000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - Diamond Sani-21 PVC sewer pipe &amp; fittings, cleanouts, Star Pipe covers, marking tape (pkg Section 2). CHA (Chris Manes) REVISE &amp; RESUBMIT 10/1/2026 (same review as SUB-003): sanitary sewer mains to be DIP. PSI response to Coles issued 10/5/2026 - resubmit with full PSI-0001 package as Rev 1.</t>
+  </si>
+  <si>
+    <t>SUB-004_R0_Original_Procore_Export_2026-10-01.pdf; SUB-004_R0_Sanitary_Section_Only.pdf; Submittal-004_Transmittal_Packaged.pdf; SUB-004_R0_CHA_Reviewed_Export_R&amp;R_2026-10-05.pdf; SUB-004_R0_CHA_Reviewed_Sanitary_Section_R&amp;R_2026-10-01.pdf; SUB-004_R0_Response_to_Coles_R&amp;R_2026-10-05.pdf (response + CHA form + sanitary section, 16 pp) - folder: documents\submittals\SUB-004 - 333000 Sanitary Sewer</t>
+  </si>
+  <si>
+    <t>Domestic Water &amp; Irrigation Rev 0 (Procore 33 1000-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - PVC pressure pipe &amp; DI fittings, 2in taps, 2in DCV, irrigation, 2in RPZ (pkg Section 3). CHA (Chris Manes) REVISE &amp; RESUBMIT 10/1/2026 (same review as SUB-003): 3in water main to meet AWWA C900 (D2241 submitted); irrigation tap/meter/BFP/main is 1in per approved plans (2in submitted). PSI response to Coles issued 10/5/2026 - resubmit with full PSI-0001 package as Rev 1.</t>
+  </si>
+  <si>
+    <t>SUB-005_R0_Original_Procore_Export_2026-10-01.pdf; SUB-005_R0_Domestic_Water_Section_Only.pdf; Submittal-005_Transmittal_Packaged.pdf; SUB-005_R0_CHA_Reviewed_Export_R&amp;R_2026-10-05.pdf; SUB-005_R0_CHA_Reviewed_Water_Section_R&amp;R_2026-10-01.pdf; SUB-005_R0_Response_to_Coles_R&amp;R_2026-10-05.pdf (response + CHA form + water section, 38 pp) - folder: documents\submittals\SUB-005 - 331000 Domestic Water</t>
+  </si>
+  <si>
+    <t>Fire Main Rev 0 (Procore 33-1.0, Package #1 Site Utilities / Fieldwire PSI-0001) - U.S. Pipe Tyton DI pipe &amp; fittings, tapping sleeve, M&amp;H 129 hydrant, 8in DCDA BFP vault, 8in PIV, 8in gate valve (pkg Section 4). CHA (Chris Manes) REVISE &amp; RESUBMIT 10/1/2026 (same package review as SUB-003, reviewed set now attached in Procore) - NO comments on fire main; R&amp;R because package resubmittal required. PSI response to Coles issued 10/5/2026 - include fire main unchanged in Rev 1.</t>
+  </si>
+  <si>
+    <t>SUB-006_R0_Procore_Cover_Only_2026-10-01.pdf; SUB-006_R0_Fire_Main_Section_REFERENCE_from_PSI-0001.pdf; Submittal-006_Transmittal_Packaged.pdf; SUB-006_R0_CHA_Reviewed_Export_R&amp;R_2026-10-05.pdf; SUB-006_R0_CHA_Reviewed_Fire_Section_R&amp;R_2026-10-01.pdf; SUB-006_R0_Response_to_Coles_R&amp;R_2026-10-05.pdf (response + CHA form + fire section, 42 pp) - folder: documents\submittals\SUB-006 - 33 Fire Main</t>
   </si>
 </sst>
 </file>
@@ -3992,7 +3998,7 @@
       </c>
       <c r="C30" s="9">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
@@ -18319,19 +18325,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="B5" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C5" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D5" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E5" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -18340,27 +18346,27 @@
         <v>46036</v>
       </c>
       <c r="L5" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M5" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="B6" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C6" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D6" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -18369,24 +18375,24 @@
         <v>46036</v>
       </c>
       <c r="L6" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M6" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B7" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C7" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D7" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -18395,27 +18401,27 @@
         <v>46008</v>
       </c>
       <c r="L7" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M7" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="B8" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C8" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D8" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E8" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -18424,30 +18430,30 @@
         <v>46170</v>
       </c>
       <c r="L8" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M8" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="B9" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C9" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D9" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E9" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F9" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -18456,24 +18462,24 @@
         <v>46170</v>
       </c>
       <c r="L9" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M9" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="B10" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C10" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D10" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -18482,24 +18488,24 @@
         <v>45968</v>
       </c>
       <c r="L10" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M10" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="B11" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C11" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D11" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -18508,24 +18514,24 @@
         <v>45968</v>
       </c>
       <c r="L11" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M11" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B12" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C12" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D12" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -18534,24 +18540,24 @@
         <v>45968</v>
       </c>
       <c r="L12" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M12" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="B13" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="C13" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D13" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -18560,24 +18566,24 @@
         <v>46008</v>
       </c>
       <c r="L13" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M13" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B14" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C14" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="D14" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -18586,30 +18592,30 @@
         <v>45968</v>
       </c>
       <c r="L14" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M14" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="B15" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C15" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D15" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E15" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F15" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -18618,30 +18624,30 @@
         <v>46170</v>
       </c>
       <c r="L15" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M15" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="B16" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C16" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D16" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E16" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F16" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -18650,24 +18656,24 @@
         <v>46170</v>
       </c>
       <c r="L16" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M16" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="B17" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C17" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D17" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -18676,24 +18682,24 @@
         <v>46008</v>
       </c>
       <c r="L17" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M17" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="B18" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="C18" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D18" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -18702,30 +18708,30 @@
         <v>46008</v>
       </c>
       <c r="L18" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M18" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="B19" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C19" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D19" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E19" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F19" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -18734,27 +18740,27 @@
         <v>46170</v>
       </c>
       <c r="L19" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M19" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="B20" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C20" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D20" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E20" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -18763,27 +18769,27 @@
         <v>46170</v>
       </c>
       <c r="L20" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M20" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="B21" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C21" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D21" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E21" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -18792,27 +18798,27 @@
         <v>46170</v>
       </c>
       <c r="L21" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M21" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="B22" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C22" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D22" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E22" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -18821,27 +18827,27 @@
         <v>46170</v>
       </c>
       <c r="L22" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M22" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="B23" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C23" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D23" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E23" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -18850,24 +18856,24 @@
         <v>46170</v>
       </c>
       <c r="L23" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M23" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B24" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C24" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D24" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -18876,24 +18882,24 @@
         <v>45968</v>
       </c>
       <c r="L24" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M24" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="B25" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C25" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D25" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -18902,24 +18908,24 @@
         <v>45968</v>
       </c>
       <c r="L25" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M25" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="B26" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C26" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D26" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -18928,24 +18934,24 @@
         <v>45968</v>
       </c>
       <c r="L26" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M26" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="B27" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C27" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D27" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -18954,27 +18960,27 @@
         <v>45968</v>
       </c>
       <c r="L27" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M27" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="B28" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C28" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D28" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E28" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -18983,27 +18989,27 @@
         <v>46170</v>
       </c>
       <c r="L28" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M28" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="B29" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C29" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D29" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E29" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -19012,24 +19018,24 @@
         <v>46036</v>
       </c>
       <c r="L29" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M29" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="B30" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C30" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D30" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -19038,27 +19044,27 @@
         <v>45968</v>
       </c>
       <c r="L30" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M30" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="B31" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D31" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E31" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -19067,27 +19073,27 @@
         <v>46170</v>
       </c>
       <c r="L31" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M31" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B32" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C32" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D32" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E32" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -19096,27 +19102,27 @@
         <v>46170</v>
       </c>
       <c r="L32" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M32" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="B33" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C33" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D33" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="E33" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -19125,24 +19131,24 @@
         <v>45908</v>
       </c>
       <c r="L33" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="M33" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="B34" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C34" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D34" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -19151,24 +19157,24 @@
         <v>46008</v>
       </c>
       <c r="L34" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M34" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="B35" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C35" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D35" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -19177,24 +19183,24 @@
         <v>45968</v>
       </c>
       <c r="L35" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M35" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="B36" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="C36" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D36" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -19203,24 +19209,24 @@
         <v>45968</v>
       </c>
       <c r="L36" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M36" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="B37" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C37" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D37" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -19229,24 +19235,24 @@
         <v>45968</v>
       </c>
       <c r="L37" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M37" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="B38" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C38" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D38" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -19255,24 +19261,24 @@
         <v>45968</v>
       </c>
       <c r="L38" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M38" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="B39" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C39" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D39" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -19281,24 +19287,24 @@
         <v>45968</v>
       </c>
       <c r="L39" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M39" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="B40" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C40" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D40" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -19307,24 +19313,24 @@
         <v>45968</v>
       </c>
       <c r="L40" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M40" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="B41" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C41" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D41" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -19333,24 +19339,24 @@
         <v>45968</v>
       </c>
       <c r="L41" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M41" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="B42" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C42" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D42" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -19359,24 +19365,24 @@
         <v>45968</v>
       </c>
       <c r="L42" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M42" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="B43" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="C43" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D43" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -19385,24 +19391,24 @@
         <v>45968</v>
       </c>
       <c r="L43" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M43" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="B44" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C44" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D44" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -19411,24 +19417,24 @@
         <v>45968</v>
       </c>
       <c r="L44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M44" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="B45" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C45" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D45" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -19437,24 +19443,24 @@
         <v>45968</v>
       </c>
       <c r="L45" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M45" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="B46" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="C46" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D46" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -19463,24 +19469,24 @@
         <v>45968</v>
       </c>
       <c r="L46" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M46" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="B47" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C47" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D47" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -19489,24 +19495,24 @@
         <v>45968</v>
       </c>
       <c r="L47" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M47" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="B48" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="C48" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D48" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -19515,27 +19521,27 @@
         <v>45968</v>
       </c>
       <c r="L48" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M48" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="B49" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="C49" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D49" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E49" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -19544,27 +19550,27 @@
         <v>46036</v>
       </c>
       <c r="L49" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M49" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="B50" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="C50" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D50" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E50" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -19573,24 +19579,24 @@
         <v>46170</v>
       </c>
       <c r="L50" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M50" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="B51" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C51" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D51" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -19599,24 +19605,24 @@
         <v>45968</v>
       </c>
       <c r="L51" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M51" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="B52" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C52" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D52" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -19625,30 +19631,30 @@
         <v>45968</v>
       </c>
       <c r="L52" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M52" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="B53" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="C53" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D53" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E53" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F53" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -19657,30 +19663,30 @@
         <v>46170</v>
       </c>
       <c r="L53" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M53" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="B54" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="C54" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D54" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E54" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F54" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -19689,24 +19695,24 @@
         <v>46170</v>
       </c>
       <c r="L54" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M54" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="B55" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="C55" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D55" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -19715,24 +19721,24 @@
         <v>45968</v>
       </c>
       <c r="L55" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M55" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="B56" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C56" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D56" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -19741,24 +19747,24 @@
         <v>46009</v>
       </c>
       <c r="L56" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M56" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="B57" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C57" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D57" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -19767,30 +19773,30 @@
         <v>45968</v>
       </c>
       <c r="L57" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M57" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="B58" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C58" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D58" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E58" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="F58" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -19799,30 +19805,30 @@
         <v>46170</v>
       </c>
       <c r="L58" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M58" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="B59" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C59" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D59" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E59" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="F59" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -19831,24 +19837,24 @@
         <v>46170</v>
       </c>
       <c r="L59" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M59" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="B60" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="C60" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D60" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -19857,24 +19863,24 @@
         <v>45968</v>
       </c>
       <c r="L60" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M60" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="B61" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C61" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D61" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -19883,24 +19889,24 @@
         <v>46009</v>
       </c>
       <c r="L61" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M61" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="B62" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C62" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D62" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -19909,24 +19915,24 @@
         <v>46009</v>
       </c>
       <c r="L62" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M62" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="B63" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C63" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D63" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -19935,24 +19941,24 @@
         <v>46009</v>
       </c>
       <c r="L63" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M63" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="B64" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C64" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D64" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -19961,24 +19967,24 @@
         <v>46009</v>
       </c>
       <c r="L64" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M64" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="B65" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C65" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D65" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -19987,24 +19993,24 @@
         <v>46009</v>
       </c>
       <c r="L65" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M65" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="B66" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C66" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D66" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -20013,24 +20019,24 @@
         <v>46009</v>
       </c>
       <c r="L66" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M66" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B67" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C67" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="D67" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -20039,24 +20045,24 @@
         <v>45968</v>
       </c>
       <c r="L67" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M67" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B68" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C68" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D68" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -20065,27 +20071,27 @@
         <v>45968</v>
       </c>
       <c r="L68" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M68" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="B69" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C69" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D69" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E69" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -20094,27 +20100,27 @@
         <v>46170</v>
       </c>
       <c r="L69" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M69" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="B70" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="C70" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D70" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E70" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -20123,27 +20129,27 @@
         <v>46170</v>
       </c>
       <c r="L70" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M70" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="B71" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="C71" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D71" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E71" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -20152,27 +20158,27 @@
         <v>46170</v>
       </c>
       <c r="L71" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M71" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="B72" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="C72" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D72" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="E72" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -20181,27 +20187,27 @@
         <v>45968</v>
       </c>
       <c r="L72" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="M72" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="B73" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="C73" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D73" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E73" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -20210,24 +20216,24 @@
         <v>46170</v>
       </c>
       <c r="L73" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M73" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="B74" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="C74" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D74" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -20236,24 +20242,24 @@
         <v>45968</v>
       </c>
       <c r="L74" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M74" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="B75" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="C75" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D75" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -20262,24 +20268,24 @@
         <v>45968</v>
       </c>
       <c r="L75" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M75" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="B76" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="C76" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D76" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -20288,24 +20294,24 @@
         <v>45968</v>
       </c>
       <c r="L76" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M76" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="B77" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C77" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D77" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -20314,24 +20320,24 @@
         <v>46009</v>
       </c>
       <c r="L77" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="B78" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C78" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D78" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -20340,24 +20346,24 @@
         <v>46009</v>
       </c>
       <c r="L78" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M78" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="B79" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="C79" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D79" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -20366,27 +20372,27 @@
         <v>45968</v>
       </c>
       <c r="L79" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M79" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B80" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="C80" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D80" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E80" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -20395,24 +20401,24 @@
         <v>46170</v>
       </c>
       <c r="L80" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M80" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="B81" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C81" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D81" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -20421,27 +20427,27 @@
         <v>45968</v>
       </c>
       <c r="L81" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M81" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="B82" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="C82" t="s">
+        <v>775</v>
+      </c>
+      <c r="D82" t="s">
+        <v>573</v>
+      </c>
+      <c r="E82" t="s">
         <v>785</v>
-      </c>
-      <c r="D82" t="s">
-        <v>583</v>
-      </c>
-      <c r="E82" t="s">
-        <v>795</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -20450,30 +20456,30 @@
         <v>46170</v>
       </c>
       <c r="L82" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M82" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="B83" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="C83" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D83" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E83" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F83" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="J83">
         <v>2</v>
@@ -20482,24 +20488,24 @@
         <v>46170</v>
       </c>
       <c r="L83" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M83" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="B84" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C84" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D84" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -20508,24 +20514,24 @@
         <v>46009</v>
       </c>
       <c r="L84" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M84" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="B85" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="C85" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="D85" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -20534,27 +20540,27 @@
         <v>45968</v>
       </c>
       <c r="L85" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M85" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B86" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C86" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="D86" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E86" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -20563,24 +20569,24 @@
         <v>46170</v>
       </c>
       <c r="L86" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M86" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B87" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="C87" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="D87" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -20589,24 +20595,24 @@
         <v>45968</v>
       </c>
       <c r="L87" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M87" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="B88" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C88" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D88" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -20615,30 +20621,30 @@
         <v>46009</v>
       </c>
       <c r="L88" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M88" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="B89" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C89" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D89" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E89" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F89" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="J89">
         <v>2</v>
@@ -20647,33 +20653,33 @@
         <v>46036</v>
       </c>
       <c r="L89" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M89" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B90" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C90" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D90" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E90" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F90" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="G90" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="J90">
         <v>3</v>
@@ -20682,27 +20688,27 @@
         <v>46233</v>
       </c>
       <c r="L90" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="B91" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="C91" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D91" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E91" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -20711,24 +20717,24 @@
         <v>46009</v>
       </c>
       <c r="L91" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M91" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="B92" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C92" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D92" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -20737,27 +20743,27 @@
         <v>46009</v>
       </c>
       <c r="L92" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M92" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="B93" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="C93" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D93" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E93" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -20766,30 +20772,30 @@
         <v>46170</v>
       </c>
       <c r="L93" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M93" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="B94" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="C94" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D94" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E94" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F94" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -20798,27 +20804,27 @@
         <v>46170</v>
       </c>
       <c r="L94" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M94" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="B95" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="C95" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D95" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E95" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -20827,33 +20833,33 @@
         <v>46170</v>
       </c>
       <c r="L95" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M95" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="B96" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="C96" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D96" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E96" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F96" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G96" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="J96">
         <v>3</v>
@@ -20862,30 +20868,30 @@
         <v>46170</v>
       </c>
       <c r="L96" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M96" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="B97" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C97" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D97" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E97" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="F97" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -20894,33 +20900,33 @@
         <v>46233</v>
       </c>
       <c r="L97" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M97" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="B98" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C98" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D98" t="s">
+        <v>573</v>
+      </c>
+      <c r="E98" t="s">
+        <v>574</v>
+      </c>
+      <c r="F98" t="s">
         <v>583</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>584</v>
-      </c>
-      <c r="F98" t="s">
-        <v>593</v>
-      </c>
-      <c r="G98" t="s">
-        <v>594</v>
       </c>
       <c r="J98">
         <v>3</v>
@@ -20929,27 +20935,27 @@
         <v>46233</v>
       </c>
       <c r="L98" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M98" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="B99" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C99" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D99" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E99" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -20958,27 +20964,27 @@
         <v>46170</v>
       </c>
       <c r="L99" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M99" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="B100" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="C100" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D100" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E100" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -20987,27 +20993,27 @@
         <v>46009</v>
       </c>
       <c r="L100" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M100" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="B101" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="C101" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D101" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E101" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -21016,30 +21022,30 @@
         <v>46009</v>
       </c>
       <c r="L101" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M101" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="B102" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C102" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D102" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E102" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="F102" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="J102">
         <v>2</v>
@@ -21048,33 +21054,33 @@
         <v>46233</v>
       </c>
       <c r="L102" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M102" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="B103" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="C103" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D103" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E103" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="F103" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G103" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="J103">
         <v>3</v>
@@ -21083,24 +21089,24 @@
         <v>46233</v>
       </c>
       <c r="L103" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M103" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="B104" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="C104" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D104" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -21109,24 +21115,24 @@
         <v>46009</v>
       </c>
       <c r="L104" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M104" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="B105" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="C105" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D105" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -21135,27 +21141,27 @@
         <v>46009</v>
       </c>
       <c r="L105" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M105" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="B106" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C106" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D106" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E106" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J106">
         <v>1</v>
@@ -21164,27 +21170,27 @@
         <v>46009</v>
       </c>
       <c r="L106" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M106" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="B107" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C107" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D107" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E107" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J107">
         <v>1</v>
@@ -21193,27 +21199,27 @@
         <v>46009</v>
       </c>
       <c r="L107" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M107" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B108" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C108" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D108" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E108" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -21222,27 +21228,27 @@
         <v>46009</v>
       </c>
       <c r="L108" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M108" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="B109" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C109" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D109" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E109" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -21251,27 +21257,27 @@
         <v>46009</v>
       </c>
       <c r="L109" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M109" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="B110" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="C110" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D110" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E110" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J110">
         <v>1</v>
@@ -21280,27 +21286,27 @@
         <v>46009</v>
       </c>
       <c r="L110" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M110" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="B111" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="C111" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D111" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E111" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J111">
         <v>1</v>
@@ -21309,27 +21315,27 @@
         <v>46009</v>
       </c>
       <c r="L111" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M111" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="B112" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C112" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="D112" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E112" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -21338,27 +21344,27 @@
         <v>46009</v>
       </c>
       <c r="L112" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M112" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="B113" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="C113" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="D113" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E113" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="J113">
         <v>1</v>
@@ -21367,27 +21373,27 @@
         <v>46009</v>
       </c>
       <c r="L113" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M113" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="B114" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
       <c r="C114" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D114" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E114" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -21396,36 +21402,36 @@
         <v>46009</v>
       </c>
       <c r="L114" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M114" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="B115" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C115" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D115" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E115" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F115" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G115" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="H115" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="J115">
         <v>4</v>
@@ -21434,33 +21440,33 @@
         <v>46233</v>
       </c>
       <c r="L115" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M115" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="B116" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="C116" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D116" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E116" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F116" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G116" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="J116">
         <v>3</v>
@@ -21469,27 +21475,27 @@
         <v>46170</v>
       </c>
       <c r="L116" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M116" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="B117" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="C117" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D117" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E117" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -21498,27 +21504,27 @@
         <v>46009</v>
       </c>
       <c r="L117" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M117" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="B118" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="C118" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D118" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E118" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -21527,27 +21533,27 @@
         <v>46009</v>
       </c>
       <c r="L118" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M118" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="B119" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="C119" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D119" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="E119" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -21556,27 +21562,27 @@
         <v>45968</v>
       </c>
       <c r="L119" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="M119" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="B120" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="C120" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D120" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="E120" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -21585,24 +21591,24 @@
         <v>45968</v>
       </c>
       <c r="L120" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="M120" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="B121" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C121" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D121" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -21611,30 +21617,30 @@
         <v>45968</v>
       </c>
       <c r="L121" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M121" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="B122" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="C122" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D122" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E122" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
       <c r="F122" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="J122">
         <v>2</v>
@@ -21643,24 +21649,24 @@
         <v>46170</v>
       </c>
       <c r="L122" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M122" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="B123" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="C123" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D123" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -21669,24 +21675,24 @@
         <v>45968</v>
       </c>
       <c r="L123" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M123" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="B124" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="C124" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D124" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -21695,24 +21701,24 @@
         <v>45968</v>
       </c>
       <c r="L124" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M124" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="B125" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="C125" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D125" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -21721,24 +21727,24 @@
         <v>45968</v>
       </c>
       <c r="L125" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M125" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="B126" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
       <c r="C126" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D126" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -21747,27 +21753,27 @@
         <v>45968</v>
       </c>
       <c r="L126" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M126" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="B127" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="C127" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D127" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="E127" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="J127">
         <v>1</v>
@@ -21776,24 +21782,24 @@
         <v>46170</v>
       </c>
       <c r="L127" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M127" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
       <c r="B128" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="C128" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D128" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -21802,24 +21808,24 @@
         <v>45968</v>
       </c>
       <c r="L128" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M128" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B129" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="C129" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D129" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -21828,10 +21834,10 @@
         <v>45968</v>
       </c>
       <c r="L129" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M129" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
@@ -22747,7 +22753,7 @@
       </c>
       <c r="C21" s="23">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
@@ -22813,7 +22819,7 @@
       </c>
       <c r="C7" s="13">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -22864,7 +22870,7 @@
       </c>
       <c r="C15" s="4">
         <f>COUNTIFS('Submittal Log'!G2:G299,"&lt;&gt;",'Submittal Log'!I2:I299,"")</f>
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
@@ -22873,7 +22879,7 @@
       </c>
       <c r="C16" s="4">
         <f>COUNTIF('Submittal Log'!J2:J299,"Revise &amp; Resubmit")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
@@ -23164,7 +23170,7 @@
       </c>
       <c r="C52" s="4">
         <f ca="1">COUNTIF('Submittal Log'!P2:P299,"&gt;=14")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -29233,13 +29239,13 @@
         <v>522</v>
       </c>
       <c r="C4" t="s">
-        <v>523</v>
+        <v>898</v>
       </c>
       <c r="D4" t="s">
         <v>515</v>
       </c>
       <c r="E4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F4" s="25">
         <v>46260</v>
@@ -29250,43 +29256,46 @@
       <c r="H4" s="25">
         <v>46274</v>
       </c>
+      <c r="I4" s="25">
+        <v>46296</v>
+      </c>
       <c r="J4" t="s">
-        <v>525</v>
+        <v>897</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>526</v>
+        <v>899</v>
       </c>
       <c r="N4" t="s">
         <v>274</v>
       </c>
       <c r="O4" s="13">
         <f t="shared" si="1"/>
-        <v>46274</v>
+        <v>46296</v>
       </c>
       <c r="P4">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>522</v>
       </c>
       <c r="C5" t="s">
-        <v>530</v>
+        <v>901</v>
       </c>
       <c r="D5" t="s">
         <v>515</v>
       </c>
       <c r="E5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F5" s="25">
         <v>46260</v>
@@ -29297,43 +29306,46 @@
       <c r="H5" s="25">
         <v>46276</v>
       </c>
+      <c r="I5" s="25">
+        <v>46296</v>
+      </c>
       <c r="J5" t="s">
-        <v>525</v>
+        <v>900</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>529</v>
+        <v>902</v>
       </c>
       <c r="N5" t="s">
         <v>274</v>
       </c>
       <c r="O5" s="13">
         <f t="shared" si="1"/>
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="P5">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>533</v>
+        <v>903</v>
       </c>
       <c r="D6" t="s">
         <v>515</v>
       </c>
       <c r="E6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F6" s="25">
         <v>46260</v>
@@ -29344,43 +29356,46 @@
       <c r="H6" s="25">
         <v>46276</v>
       </c>
+      <c r="I6" s="25">
+        <v>46296</v>
+      </c>
       <c r="J6" t="s">
-        <v>525</v>
+        <v>900</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>534</v>
+        <v>904</v>
       </c>
       <c r="N6" t="s">
         <v>274</v>
       </c>
       <c r="O6" s="13">
         <f t="shared" si="1"/>
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="P6">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C7" t="s">
-        <v>537</v>
+        <v>905</v>
       </c>
       <c r="D7" t="s">
         <v>515</v>
       </c>
       <c r="E7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F7" s="25">
         <v>46260</v>
@@ -29391,43 +29406,46 @@
       <c r="H7" s="25">
         <v>46276</v>
       </c>
+      <c r="I7" s="25">
+        <v>46296</v>
+      </c>
       <c r="J7" t="s">
-        <v>525</v>
+        <v>900</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>538</v>
+        <v>906</v>
       </c>
       <c r="N7" t="s">
         <v>274</v>
       </c>
       <c r="O7" s="13">
         <f t="shared" si="1"/>
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="P7">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C8" t="s">
-        <v>541</v>
+        <v>907</v>
       </c>
       <c r="D8" t="s">
         <v>515</v>
       </c>
       <c r="E8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F8" s="25">
         <v>46260</v>
@@ -29438,43 +29456,46 @@
       <c r="H8" s="25">
         <v>46276</v>
       </c>
+      <c r="I8" s="25">
+        <v>46296</v>
+      </c>
       <c r="J8" t="s">
-        <v>525</v>
+        <v>900</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>542</v>
+        <v>908</v>
       </c>
       <c r="N8" t="s">
         <v>274</v>
       </c>
       <c r="O8" s="13">
         <f t="shared" si="1"/>
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="P8">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C9" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="D9" t="s">
         <v>515</v>
       </c>
       <c r="E9" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F9" s="25">
         <v>46260</v>
@@ -29496,7 +29517,7 @@
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="N9" t="s">
         <v>274</v>
@@ -29512,19 +29533,19 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C10" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="D10" t="s">
         <v>515</v>
       </c>
       <c r="E10" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="F10" s="25">
         <v>46265</v>
@@ -29536,14 +29557,14 @@
         <v>46290</v>
       </c>
       <c r="J10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="N10" t="s">
         <v>274</v>
@@ -29554,24 +29575,24 @@
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C11" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D11" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E11" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="F11" s="25">
         <v>46265</v>
@@ -29583,14 +29604,14 @@
         <v>46290</v>
       </c>
       <c r="J11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M11" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="N11" t="s">
         <v>274</v>
@@ -29601,24 +29622,24 @@
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="C12" t="s">
         <v>549</v>
-      </c>
-      <c r="C12" t="s">
-        <v>559</v>
       </c>
       <c r="D12" t="s">
         <v>515</v>
       </c>
       <c r="E12" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="F12" s="25">
         <v>46265</v>
@@ -29630,14 +29651,14 @@
         <v>46290</v>
       </c>
       <c r="J12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="N12" t="s">
         <v>274</v>
@@ -29648,7 +29669,7 @@
       </c>
       <c r="P12">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -33766,19 +33787,19 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="B2" s="25">
         <v>46254</v>
       </c>
       <c r="C2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D2" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="E2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="H2">
         <v>99986.52</v>
@@ -33787,14 +33808,14 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M2">
         <f>IF(A2="","",SUMIFS(H$2:H2,J$2:J2,"Approved"))</f>
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="O2" t="s">
         <v>274</v>
@@ -33805,27 +33826,27 @@
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q65" ca="1" si="1">IF(A2="","",IF(OR(J2="Approved",J2="Rejected",J2="Void"),"",TODAY()-P2))</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="B3" s="25">
         <v>46259</v>
       </c>
       <c r="C3" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="D3" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="E3" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -33834,14 +33855,14 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M3">
         <f>IF(A3="","",SUMIFS(H$2:H3,J$2:J3,"Approved"))</f>
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="O3" t="s">
         <v>274</v>
@@ -33852,10 +33873,10 @@
       </c>
       <c r="Q3">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R3" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -38109,7 +38130,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="B2" s="25">
         <v>46257</v>
@@ -38121,7 +38142,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="F2">
         <v>56430</v>
@@ -38130,19 +38151,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="J2" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="K2" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="L2" s="25">
         <v>46296</v>
       </c>
       <c r="M2" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="N2">
         <v>56430</v>
@@ -38152,7 +38173,7 @@
         <v>56430</v>
       </c>
       <c r="P2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="Q2" t="s">
         <v>274</v>

--- a/tracker/Project_Control_Tracker.xlsx
+++ b/tracker/Project_Control_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\GC Grocery\4_Active_Jobs\Norcross, GA 1517 Lidl - Ground Up\17. - Claude AI\15170000GR-Norcross-GA---Lidl-US\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA806560-79ED-408F-984B-114ED0111B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3BBDF0-04C5-4EFF-BBCD-54B4A65C0F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="17085" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="17085" tabRatio="500" firstSheet="16" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="1002">
   <si>
     <t>PROJECT INFO</t>
   </si>
@@ -1515,9 +1515,6 @@
     <t>Luis F. Marcelino (Place Services Inc.); Tucker Teague (Place Services Inc.); Jens Byer; Chris Manes (CHA Consulting, Inc.); Gabriela Camarillo (Progressive Companies)</t>
   </si>
   <si>
-    <t>Mobilization and demolition start - on site Mon 10/5/2026</t>
-  </si>
-  <si>
     <t>Confirm Monday 10/5 mobilization to Jens and Chris</t>
   </si>
   <si>
@@ -1527,9 +1524,6 @@
     <t>Before 10/5/2026</t>
   </si>
   <si>
-    <t>County pre-con meetings - traffic/ROW (R.J. Haynes)</t>
-  </si>
-  <si>
     <t>Schedule county pre-con for traffic / right-of-way work</t>
   </si>
   <si>
@@ -1545,18 +1539,12 @@
     <t>Before utility work - DATE NEEDED</t>
   </si>
   <si>
-    <t>County pre-con meetings - correspondence distribution</t>
-  </si>
-  <si>
     <t>Forward county correspondence to Jens and Chris</t>
   </si>
   <si>
     <t>Ongoing</t>
   </si>
   <si>
-    <t>County inspector asked to meet team before work starts</t>
-  </si>
-  <si>
     <t>Send inspector contact information to Luis</t>
   </si>
   <si>
@@ -1569,18 +1557,9 @@
     <t>Contact inspector before starting work (including demo, if requested)</t>
   </si>
   <si>
-    <t>Civil plan revisions resubmission on hold until Phase 1 E&amp;S installed</t>
-  </si>
-  <si>
     <t>Resubmit civil plan revisions; keep team informed of timing</t>
   </si>
   <si>
-    <t>After Phase 1 E&amp;S installed - DATE NEEDED</t>
-  </si>
-  <si>
-    <t>Communication - copy Tucker Teague and Bobby McTeague on all emails</t>
-  </si>
-  <si>
     <t>Add Tucker Teague and Bobby McTeague to all project correspondence</t>
   </si>
   <si>
@@ -1590,9 +1569,6 @@
     <t>Immediately</t>
   </si>
   <si>
-    <t>Recurring OAC meeting - Thursday afternoons</t>
-  </si>
-  <si>
     <t>Send recurring Thursday-afternoon OAC invite to all attendees</t>
   </si>
   <si>
@@ -1605,30 +1581,15 @@
     <t>10/22/2026 (approx.)</t>
   </si>
   <si>
-    <t>Contract and Procore - executed contract upload</t>
-  </si>
-  <si>
     <t>Upload fully executed contract to Procore</t>
   </si>
   <si>
-    <t>Contract and Procore - inflation change item; demo/abatement against allowance</t>
-  </si>
-  <si>
     <t>Log inflation discussion in Procore as a change item</t>
   </si>
   <si>
-    <t>After contract upload - DATE NEEDED</t>
-  </si>
-  <si>
     <t>PCO pending (not yet in Change Order Log)</t>
   </si>
   <si>
-    <t>Site visit by Jens Byer within 2-3 weeks</t>
-  </si>
-  <si>
-    <t>County pre-con meetings - utility work (Cole's Construction, site contractor)</t>
-  </si>
-  <si>
     <t>Cole's Construction</t>
   </si>
   <si>
@@ -3043,6 +3004,108 @@
   </si>
   <si>
     <t>The Sec. 3.6.1 Milestone table governs: Substantial Completion 6/21/2027, Final Completion/CofO 7/26/2027, Release of Retention 8/1/2027. Sec. 3.1's 'June 14, 2027' Scheduled Date of Final Completion is inconsistent and is disregarded (confirmed by Luis Marcelino 10/8/2026).</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Mobilization and demolition start - on site Mon 10/5/2026 | 10/9/2026 update: Mobilization confirmed; abatement did not start as expected</t>
+  </si>
+  <si>
+    <t>County pre-con meetings - traffic/ROW (R.J. Haynes) | 10/9/2026 update: Awaiting R.J. Haynes confirmation</t>
+  </si>
+  <si>
+    <t>County pre-con meetings - utility work (Cole's Construction, site contractor) | 10/9/2026 update: Awaiting Cole's Construction confirmation</t>
+  </si>
+  <si>
+    <t>County pre-con meetings - correspondence distribution | 10/9/2026 update: Ongoing</t>
+  </si>
+  <si>
+    <t>County inspector asked to meet team before work starts | 10/9/2026 update: Completed</t>
+  </si>
+  <si>
+    <t>County inspector asked to meet team before work starts | 10/9/2026 update: Inspector contacted; wants BMPs in place and will schedule the pre-con</t>
+  </si>
+  <si>
+    <t>Civil plan revisions resubmission on hold until Phase 1 E&amp;S installed | 10/9/2026 update: To be submitted when BMPs are complete (scheduled early week of 10/12)</t>
+  </si>
+  <si>
+    <t>After BMPs complete - est. week of 10/12/2026</t>
+  </si>
+  <si>
+    <t>Communication - copy Tucker Teague and Bobby McTeague on all emails | 10/9/2026 update: Added</t>
+  </si>
+  <si>
+    <t>Recurring OAC meeting - Thursday afternoons | 10/9/2026 update: Completed</t>
+  </si>
+  <si>
+    <t>Site visit by Jens Byer within 2-3 weeks | 10/9/2026 update: Completed</t>
+  </si>
+  <si>
+    <t>Contract and Procore - executed contract upload | 10/9/2026 update: Completed</t>
+  </si>
+  <si>
+    <t>Contract and Procore - inflation change item; demo/abatement against allowance | 10/9/2026 update: To be completed EOD 10/9</t>
+  </si>
+  <si>
+    <t>10/9/2026</t>
+  </si>
+  <si>
+    <t>OAC-002</t>
+  </si>
+  <si>
+    <t>Abatement not started as expected - change in abatement contractor triggered new statutory notice period; claim info to Lidl 10/9</t>
+  </si>
+  <si>
+    <t>Send claim information for the abatement delay to Lidl</t>
+  </si>
+  <si>
+    <t>Claim # pending; PCO-002</t>
+  </si>
+  <si>
+    <t>documents\meeting minutes\OAC\Meeting_Minutes_OAC-002_2026-10-08.pdf</t>
+  </si>
+  <si>
+    <t>Utility disconnects - follow-up needed on existing services</t>
+  </si>
+  <si>
+    <t>Follow up on existing utility disconnects</t>
+  </si>
+  <si>
+    <t>DATE NEEDED</t>
+  </si>
+  <si>
+    <t>New utility service applications for the new building</t>
+  </si>
+  <si>
+    <t>Submit new service applications for the utilities</t>
+  </si>
+  <si>
+    <t>Progressive Companies (Gabriela Camarillo)</t>
+  </si>
+  <si>
+    <t>New site plans to be sent in</t>
+  </si>
+  <si>
+    <t>Send in new site plans</t>
+  </si>
+  <si>
+    <t>Chris Manes (CHA Consulting, Inc.)</t>
+  </si>
+  <si>
+    <t>Potential changes to current utility design layout once utility providers complete their designs</t>
+  </si>
+  <si>
+    <t>Review utility provider designs; issue any required changes to the current utility layout</t>
+  </si>
+  <si>
+    <t>After utility provider designs complete - DATE NEEDED</t>
+  </si>
+  <si>
+    <t>Bobby McTeague / Tim Mauldin</t>
+  </si>
+  <si>
+    <t>Luis F. Marcelino (Place Services Inc.); Tucker Teague (Place Services Inc.); Tim Mauldin (Place Services Inc., Superintendent); Jens Byer (Lidl US); Chris Manes (CHA Consulting, Inc.); Gabriela Camarillo (Progressive Companies); John Rischer (Lidl US)</t>
   </si>
 </sst>
 </file>
@@ -4162,7 +4225,7 @@
         <v>25</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
@@ -4235,7 +4298,7 @@
       </c>
       <c r="C30" s="9">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
@@ -4397,22 +4460,22 @@
         <v>470</v>
       </c>
       <c r="E2" t="s">
+        <v>969</v>
+      </c>
+      <c r="F2" t="s">
         <v>471</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>472</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="23" t="s">
         <v>473</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>474</v>
-      </c>
       <c r="I2" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
       <c r="K2" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -4429,16 +4492,16 @@
         <v>470</v>
       </c>
       <c r="E3" t="s">
+        <v>970</v>
+      </c>
+      <c r="F3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G3" t="s">
         <v>475</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="23" t="s">
         <v>476</v>
-      </c>
-      <c r="G3" t="s">
-        <v>477</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>478</v>
       </c>
       <c r="I3" t="s">
         <v>469</v>
@@ -4461,16 +4524,16 @@
         <v>470</v>
       </c>
       <c r="E4" t="s">
-        <v>508</v>
+        <v>971</v>
       </c>
       <c r="F4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G4" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I4" t="s">
         <v>469</v>
@@ -4490,16 +4553,16 @@
         <v>470</v>
       </c>
       <c r="E5" t="s">
-        <v>481</v>
+        <v>972</v>
       </c>
       <c r="F5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G5" t="s">
-        <v>473</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I5" t="s">
         <v>469</v>
@@ -4519,19 +4582,19 @@
         <v>470</v>
       </c>
       <c r="E6" t="s">
-        <v>484</v>
+        <v>973</v>
       </c>
       <c r="F6" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="I6" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -4548,19 +4611,19 @@
         <v>470</v>
       </c>
       <c r="E7" t="s">
+        <v>974</v>
+      </c>
+      <c r="F7" t="s">
         <v>484</v>
       </c>
-      <c r="F7" t="s">
-        <v>488</v>
-      </c>
       <c r="G7" t="s">
+        <v>472</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>473</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>474</v>
-      </c>
       <c r="I7" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -4577,16 +4640,16 @@
         <v>470</v>
       </c>
       <c r="E8" t="s">
-        <v>489</v>
+        <v>975</v>
       </c>
       <c r="F8" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>491</v>
+        <v>976</v>
       </c>
       <c r="I8" t="s">
         <v>469</v>
@@ -4606,19 +4669,19 @@
         <v>470</v>
       </c>
       <c r="E9" t="s">
-        <v>492</v>
+        <v>977</v>
       </c>
       <c r="F9" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="G9" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I9" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -4635,19 +4698,19 @@
         <v>470</v>
       </c>
       <c r="E10" t="s">
-        <v>496</v>
+        <v>978</v>
       </c>
       <c r="F10" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G10" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H10" s="13">
         <v>46303</v>
       </c>
       <c r="I10" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -4664,19 +4727,19 @@
         <v>470</v>
       </c>
       <c r="E11" t="s">
-        <v>507</v>
+        <v>979</v>
       </c>
       <c r="F11" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G11" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="I11" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -4693,19 +4756,19 @@
         <v>470</v>
       </c>
       <c r="E12" t="s">
-        <v>501</v>
+        <v>980</v>
       </c>
       <c r="F12" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="G12" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="I12" t="s">
-        <v>469</v>
+        <v>968</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -4722,22 +4785,173 @@
         <v>470</v>
       </c>
       <c r="E13" t="s">
-        <v>503</v>
+        <v>981</v>
       </c>
       <c r="F13" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="G13" t="s">
-        <v>473</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>505</v>
+        <v>982</v>
       </c>
       <c r="I13" t="s">
         <v>469</v>
       </c>
       <c r="J13" t="s">
-        <v>506</v>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>983</v>
+      </c>
+      <c r="B14" s="24">
+        <v>46303</v>
+      </c>
+      <c r="C14" t="s">
+        <v>468</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E14" t="s">
+        <v>984</v>
+      </c>
+      <c r="F14" t="s">
+        <v>985</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="24">
+        <v>46304</v>
+      </c>
+      <c r="I14" t="s">
+        <v>469</v>
+      </c>
+      <c r="J14" t="s">
+        <v>986</v>
+      </c>
+      <c r="K14" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>983</v>
+      </c>
+      <c r="B15" s="24">
+        <v>46303</v>
+      </c>
+      <c r="C15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E15" t="s">
+        <v>988</v>
+      </c>
+      <c r="F15" t="s">
+        <v>989</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>990</v>
+      </c>
+      <c r="I15" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>983</v>
+      </c>
+      <c r="B16" s="24">
+        <v>46303</v>
+      </c>
+      <c r="C16" t="s">
+        <v>468</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E16" t="s">
+        <v>991</v>
+      </c>
+      <c r="F16" t="s">
+        <v>992</v>
+      </c>
+      <c r="G16" t="s">
+        <v>993</v>
+      </c>
+      <c r="H16" t="s">
+        <v>990</v>
+      </c>
+      <c r="I16" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>983</v>
+      </c>
+      <c r="B17" s="24">
+        <v>46303</v>
+      </c>
+      <c r="C17" t="s">
+        <v>468</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E17" t="s">
+        <v>994</v>
+      </c>
+      <c r="F17" t="s">
+        <v>995</v>
+      </c>
+      <c r="G17" t="s">
+        <v>996</v>
+      </c>
+      <c r="H17" t="s">
+        <v>990</v>
+      </c>
+      <c r="I17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>983</v>
+      </c>
+      <c r="B18" s="24">
+        <v>46303</v>
+      </c>
+      <c r="C18" t="s">
+        <v>468</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E18" t="s">
+        <v>997</v>
+      </c>
+      <c r="F18" t="s">
+        <v>998</v>
+      </c>
+      <c r="G18" t="s">
+        <v>996</v>
+      </c>
+      <c r="H18" t="s">
+        <v>999</v>
+      </c>
+      <c r="I18" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
@@ -7929,7 +8143,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="B2" s="24">
         <v>46300</v>
@@ -7939,15 +8153,15 @@
         <v>Missed</v>
       </c>
       <c r="E2" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F2" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="B3" s="24">
         <v>46314</v>
@@ -7957,15 +8171,15 @@
         <v>Due Soon</v>
       </c>
       <c r="E3" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F3" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="B4" s="24">
         <v>46353</v>
@@ -7975,15 +8189,15 @@
         <v>On Track</v>
       </c>
       <c r="E4" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F4" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="B5" s="24">
         <v>46381</v>
@@ -7993,15 +8207,15 @@
         <v>On Track</v>
       </c>
       <c r="E5" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F5" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="B6" s="24">
         <v>46414</v>
@@ -8011,15 +8225,15 @@
         <v>On Track</v>
       </c>
       <c r="E6" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F6" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="B7" s="24">
         <v>46437</v>
@@ -8029,15 +8243,15 @@
         <v>On Track</v>
       </c>
       <c r="E7" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F7" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="B8" s="24">
         <v>46458</v>
@@ -8047,15 +8261,15 @@
         <v>On Track</v>
       </c>
       <c r="E8" t="s">
+        <v>927</v>
+      </c>
+      <c r="F8" t="s">
         <v>940</v>
-      </c>
-      <c r="F8" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="B9" s="24">
         <v>46472</v>
@@ -8065,15 +8279,15 @@
         <v>On Track</v>
       </c>
       <c r="E9" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F9" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="B10" s="24">
         <v>46524</v>
@@ -8083,15 +8297,15 @@
         <v>On Track</v>
       </c>
       <c r="E10" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F10" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="B11" s="24">
         <v>46506</v>
@@ -8101,15 +8315,15 @@
         <v>On Track</v>
       </c>
       <c r="E11" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F11" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="B12" s="24">
         <v>46559</v>
@@ -8119,15 +8333,15 @@
         <v>On Track</v>
       </c>
       <c r="E12" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F12" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="B13" s="24">
         <v>46566</v>
@@ -8137,15 +8351,15 @@
         <v>On Track</v>
       </c>
       <c r="E13" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F13" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="B14" s="24">
         <v>46587</v>
@@ -8155,15 +8369,15 @@
         <v>On Track</v>
       </c>
       <c r="E14" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F14" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="B15" s="24">
         <v>46594</v>
@@ -8173,15 +8387,15 @@
         <v>On Track</v>
       </c>
       <c r="E15" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F15" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="B16" s="24">
         <v>46600</v>
@@ -8191,15 +8405,15 @@
         <v>On Track</v>
       </c>
       <c r="E16" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F16" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
       <c r="B17" s="24">
         <v>46320</v>
@@ -8209,15 +8423,15 @@
         <v>On Track</v>
       </c>
       <c r="E17" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F17" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>971</v>
+        <v>958</v>
       </c>
       <c r="B18" s="24">
         <v>46564</v>
@@ -8227,15 +8441,15 @@
         <v>On Track</v>
       </c>
       <c r="E18" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F18" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="B19" s="24">
         <v>46614</v>
@@ -8245,15 +8459,15 @@
         <v>On Track</v>
       </c>
       <c r="E19" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F19" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="B20" s="24">
         <v>46624</v>
@@ -8263,10 +8477,10 @@
         <v>On Track</v>
       </c>
       <c r="E20" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="F20" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -18784,19 +18998,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="B5" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C5" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D5" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E5" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -18805,27 +19019,27 @@
         <v>46036</v>
       </c>
       <c r="L5" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M5" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="B6" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C6" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D6" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E6" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -18834,24 +19048,24 @@
         <v>46036</v>
       </c>
       <c r="L6" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M6" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="B7" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="C7" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D7" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -18860,27 +19074,27 @@
         <v>46008</v>
       </c>
       <c r="L7" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M7" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="B8" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="C8" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D8" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E8" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -18889,30 +19103,30 @@
         <v>46170</v>
       </c>
       <c r="L8" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M8" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="B9" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D9" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E9" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F9" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -18921,24 +19135,24 @@
         <v>46170</v>
       </c>
       <c r="L9" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M9" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="B10" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C10" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D10" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -18947,24 +19161,24 @@
         <v>45968</v>
       </c>
       <c r="L10" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M10" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="B11" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C11" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D11" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -18973,24 +19187,24 @@
         <v>45968</v>
       </c>
       <c r="L11" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M11" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="B12" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="C12" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D12" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -18999,24 +19213,24 @@
         <v>45968</v>
       </c>
       <c r="L12" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M12" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="B13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C13" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D13" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -19025,24 +19239,24 @@
         <v>46008</v>
       </c>
       <c r="L13" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M13" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B14" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C14" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D14" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -19051,30 +19265,30 @@
         <v>45968</v>
       </c>
       <c r="L14" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M14" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="B15" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C15" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D15" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E15" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F15" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -19083,30 +19297,30 @@
         <v>46170</v>
       </c>
       <c r="L15" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M15" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="B16" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C16" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D16" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E16" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F16" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -19115,24 +19329,24 @@
         <v>46170</v>
       </c>
       <c r="L16" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M16" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="B17" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C17" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D17" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -19141,24 +19355,24 @@
         <v>46008</v>
       </c>
       <c r="L17" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M17" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="C18" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D18" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -19167,30 +19381,30 @@
         <v>46008</v>
       </c>
       <c r="L18" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M18" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="B19" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="C19" t="s">
+        <v>614</v>
+      </c>
+      <c r="D19" t="s">
+        <v>586</v>
+      </c>
+      <c r="E19" t="s">
+        <v>560</v>
+      </c>
+      <c r="F19" t="s">
         <v>627</v>
-      </c>
-      <c r="D19" t="s">
-        <v>599</v>
-      </c>
-      <c r="E19" t="s">
-        <v>573</v>
-      </c>
-      <c r="F19" t="s">
-        <v>640</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -19199,27 +19413,27 @@
         <v>46170</v>
       </c>
       <c r="L19" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M19" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="B20" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="C20" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D20" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E20" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -19228,27 +19442,27 @@
         <v>46170</v>
       </c>
       <c r="L20" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M20" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="B21" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C21" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D21" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E21" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -19257,27 +19471,27 @@
         <v>46170</v>
       </c>
       <c r="L21" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M21" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="B22" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C22" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D22" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E22" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -19286,27 +19500,27 @@
         <v>46170</v>
       </c>
       <c r="L22" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M22" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="B23" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C23" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D23" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E23" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -19315,24 +19529,24 @@
         <v>46170</v>
       </c>
       <c r="L23" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M23" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="B24" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C24" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D24" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -19341,24 +19555,24 @@
         <v>45968</v>
       </c>
       <c r="L24" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M24" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="B25" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C25" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D25" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -19367,24 +19581,24 @@
         <v>45968</v>
       </c>
       <c r="L25" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M25" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="B26" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C26" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D26" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -19393,24 +19607,24 @@
         <v>45968</v>
       </c>
       <c r="L26" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M26" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="B27" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C27" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D27" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -19419,27 +19633,27 @@
         <v>45968</v>
       </c>
       <c r="L27" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M27" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="B28" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="C28" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D28" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E28" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -19448,27 +19662,27 @@
         <v>46170</v>
       </c>
       <c r="L28" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M28" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="B29" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="C29" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D29" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E29" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -19477,24 +19691,24 @@
         <v>46036</v>
       </c>
       <c r="L29" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M29" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="B30" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C30" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D30" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -19503,27 +19717,27 @@
         <v>45968</v>
       </c>
       <c r="L30" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M30" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="B31" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C31" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D31" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E31" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -19532,27 +19746,27 @@
         <v>46170</v>
       </c>
       <c r="L31" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M31" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="B32" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C32" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D32" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E32" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -19561,27 +19775,27 @@
         <v>46170</v>
       </c>
       <c r="L32" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M32" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="B33" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="C33" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D33" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="E33" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -19590,24 +19804,24 @@
         <v>45908</v>
       </c>
       <c r="L33" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M33" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B34" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C34" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D34" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -19616,24 +19830,24 @@
         <v>46008</v>
       </c>
       <c r="L34" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M34" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="B35" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C35" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D35" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -19642,24 +19856,24 @@
         <v>45968</v>
       </c>
       <c r="L35" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M35" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="B36" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="C36" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D36" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -19668,24 +19882,24 @@
         <v>45968</v>
       </c>
       <c r="L36" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M36" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="B37" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C37" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D37" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -19694,24 +19908,24 @@
         <v>45968</v>
       </c>
       <c r="L37" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M37" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="B38" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C38" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D38" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -19720,24 +19934,24 @@
         <v>45968</v>
       </c>
       <c r="L38" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M38" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="B39" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C39" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D39" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -19746,24 +19960,24 @@
         <v>45968</v>
       </c>
       <c r="L39" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M39" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="B40" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C40" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D40" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -19772,24 +19986,24 @@
         <v>45968</v>
       </c>
       <c r="L40" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M40" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="B41" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C41" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D41" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -19798,24 +20012,24 @@
         <v>45968</v>
       </c>
       <c r="L41" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M41" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="B42" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="C42" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D42" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -19824,24 +20038,24 @@
         <v>45968</v>
       </c>
       <c r="L42" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M42" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="B43" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C43" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D43" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -19850,24 +20064,24 @@
         <v>45968</v>
       </c>
       <c r="L43" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M43" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="B44" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="C44" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D44" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -19876,24 +20090,24 @@
         <v>45968</v>
       </c>
       <c r="L44" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M44" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="B45" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="C45" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D45" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -19902,24 +20116,24 @@
         <v>45968</v>
       </c>
       <c r="L45" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M45" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="B46" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="C46" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D46" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -19928,24 +20142,24 @@
         <v>45968</v>
       </c>
       <c r="L46" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M46" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="B47" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="C47" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D47" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -19954,24 +20168,24 @@
         <v>45968</v>
       </c>
       <c r="L47" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M47" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="B48" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="C48" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D48" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -19980,27 +20194,27 @@
         <v>45968</v>
       </c>
       <c r="L48" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M48" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="B49" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D49" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E49" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -20009,27 +20223,27 @@
         <v>46036</v>
       </c>
       <c r="L49" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M49" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="B50" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C50" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D50" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E50" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -20038,24 +20252,24 @@
         <v>46170</v>
       </c>
       <c r="L50" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M50" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="B51" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="C51" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D51" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -20064,24 +20278,24 @@
         <v>45968</v>
       </c>
       <c r="L51" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M51" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="B52" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="C52" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D52" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -20090,30 +20304,30 @@
         <v>45968</v>
       </c>
       <c r="L52" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M52" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="B53" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="C53" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D53" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E53" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F53" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -20122,30 +20336,30 @@
         <v>46170</v>
       </c>
       <c r="L53" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M53" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="B54" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="C54" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D54" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E54" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F54" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -20154,24 +20368,24 @@
         <v>46170</v>
       </c>
       <c r="L54" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M54" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B55" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="C55" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D55" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -20180,24 +20394,24 @@
         <v>45968</v>
       </c>
       <c r="L55" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M55" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="B56" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C56" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D56" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -20206,24 +20420,24 @@
         <v>46009</v>
       </c>
       <c r="L56" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M56" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B57" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C57" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D57" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -20232,30 +20446,30 @@
         <v>45968</v>
       </c>
       <c r="L57" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M57" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="B58" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="C58" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D58" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E58" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="F58" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -20264,30 +20478,30 @@
         <v>46170</v>
       </c>
       <c r="L58" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M58" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="B59" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="C59" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D59" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E59" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="F59" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -20296,24 +20510,24 @@
         <v>46170</v>
       </c>
       <c r="L59" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M59" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="B60" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C60" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D60" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -20322,24 +20536,24 @@
         <v>45968</v>
       </c>
       <c r="L60" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M60" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="B61" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="C61" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D61" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -20348,24 +20562,24 @@
         <v>46009</v>
       </c>
       <c r="L61" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M61" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="B62" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="C62" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D62" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -20374,24 +20588,24 @@
         <v>46009</v>
       </c>
       <c r="L62" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M62" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="B63" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C63" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D63" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -20400,24 +20614,24 @@
         <v>46009</v>
       </c>
       <c r="L63" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M63" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="B64" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C64" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D64" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -20426,24 +20640,24 @@
         <v>46009</v>
       </c>
       <c r="L64" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M64" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B65" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C65" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D65" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -20452,24 +20666,24 @@
         <v>46009</v>
       </c>
       <c r="L65" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M65" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="B66" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C66" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D66" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -20478,24 +20692,24 @@
         <v>46009</v>
       </c>
       <c r="L66" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M66" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="B67" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C67" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D67" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -20504,24 +20718,24 @@
         <v>45968</v>
       </c>
       <c r="L67" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M67" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="B68" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="C68" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D68" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -20530,27 +20744,27 @@
         <v>45968</v>
       </c>
       <c r="L68" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M68" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="B69" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C69" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D69" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E69" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -20559,27 +20773,27 @@
         <v>46170</v>
       </c>
       <c r="L69" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M69" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="B70" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="C70" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D70" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E70" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -20588,27 +20802,27 @@
         <v>46170</v>
       </c>
       <c r="L70" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M70" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="B71" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C71" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D71" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E71" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -20617,27 +20831,27 @@
         <v>46170</v>
       </c>
       <c r="L71" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M71" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="B72" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C72" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D72" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="E72" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -20646,27 +20860,27 @@
         <v>45968</v>
       </c>
       <c r="L72" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M72" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="B73" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="C73" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D73" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E73" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -20675,24 +20889,24 @@
         <v>46170</v>
       </c>
       <c r="L73" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M73" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="B74" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="C74" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D74" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -20701,24 +20915,24 @@
         <v>45968</v>
       </c>
       <c r="L74" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M74" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="B75" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="C75" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D75" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -20727,24 +20941,24 @@
         <v>45968</v>
       </c>
       <c r="L75" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M75" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B76" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C76" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D76" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -20753,24 +20967,24 @@
         <v>45968</v>
       </c>
       <c r="L76" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M76" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="B77" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C77" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D77" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -20779,24 +20993,24 @@
         <v>46009</v>
       </c>
       <c r="L77" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M77" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="B78" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C78" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D78" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -20805,24 +21019,24 @@
         <v>46009</v>
       </c>
       <c r="L78" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M78" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="B79" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="C79" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D79" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -20831,27 +21045,27 @@
         <v>45968</v>
       </c>
       <c r="L79" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M79" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="B80" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="C80" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D80" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E80" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -20860,24 +21074,24 @@
         <v>46170</v>
       </c>
       <c r="L80" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M80" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="B81" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="C81" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D81" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -20886,27 +21100,27 @@
         <v>45968</v>
       </c>
       <c r="L81" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M81" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="B82" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="C82" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D82" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E82" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -20915,30 +21129,30 @@
         <v>46170</v>
       </c>
       <c r="L82" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M82" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="B83" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C83" t="s">
+        <v>761</v>
+      </c>
+      <c r="D83" t="s">
+        <v>559</v>
+      </c>
+      <c r="E83" t="s">
+        <v>560</v>
+      </c>
+      <c r="F83" t="s">
         <v>774</v>
-      </c>
-      <c r="D83" t="s">
-        <v>572</v>
-      </c>
-      <c r="E83" t="s">
-        <v>573</v>
-      </c>
-      <c r="F83" t="s">
-        <v>787</v>
       </c>
       <c r="J83">
         <v>2</v>
@@ -20947,24 +21161,24 @@
         <v>46170</v>
       </c>
       <c r="L83" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M83" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="B84" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="C84" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D84" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -20973,24 +21187,24 @@
         <v>46009</v>
       </c>
       <c r="L84" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M84" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="B85" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="C85" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D85" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -20999,27 +21213,27 @@
         <v>45968</v>
       </c>
       <c r="L85" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M85" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="B86" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="C86" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D86" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E86" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -21028,24 +21242,24 @@
         <v>46170</v>
       </c>
       <c r="L86" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M86" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="B87" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="C87" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D87" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -21054,24 +21268,24 @@
         <v>45968</v>
       </c>
       <c r="L87" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M87" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="B88" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C88" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D88" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -21080,30 +21294,30 @@
         <v>46009</v>
       </c>
       <c r="L88" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="B89" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="C89" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D89" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E89" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="F89" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="J89">
         <v>2</v>
@@ -21112,33 +21326,33 @@
         <v>46036</v>
       </c>
       <c r="L89" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M89" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="B90" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C90" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D90" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E90" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F90" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="G90" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="J90">
         <v>3</v>
@@ -21147,27 +21361,27 @@
         <v>46233</v>
       </c>
       <c r="L90" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M90" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="B91" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="C91" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D91" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E91" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -21176,24 +21390,24 @@
         <v>46009</v>
       </c>
       <c r="L91" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M91" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B92" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="C92" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D92" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -21202,27 +21416,27 @@
         <v>46009</v>
       </c>
       <c r="L92" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M92" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="B93" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="C93" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D93" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E93" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -21231,30 +21445,30 @@
         <v>46170</v>
       </c>
       <c r="L93" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M93" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="B94" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="C94" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D94" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E94" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F94" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -21263,27 +21477,27 @@
         <v>46170</v>
       </c>
       <c r="L94" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M94" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="B95" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="C95" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D95" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E95" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -21292,33 +21506,33 @@
         <v>46170</v>
       </c>
       <c r="L95" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M95" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="B96" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C96" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D96" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E96" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="F96" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G96" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="J96">
         <v>3</v>
@@ -21327,30 +21541,30 @@
         <v>46170</v>
       </c>
       <c r="L96" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M96" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="B97" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C97" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D97" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E97" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="F97" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -21359,33 +21573,33 @@
         <v>46233</v>
       </c>
       <c r="L97" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M97" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="B98" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C98" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D98" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E98" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F98" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="G98" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="J98">
         <v>3</v>
@@ -21394,27 +21608,27 @@
         <v>46233</v>
       </c>
       <c r="L98" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="B99" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="C99" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D99" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E99" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -21423,27 +21637,27 @@
         <v>46170</v>
       </c>
       <c r="L99" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M99" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="B100" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C100" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D100" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E100" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -21452,27 +21666,27 @@
         <v>46009</v>
       </c>
       <c r="L100" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M100" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="B101" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="C101" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D101" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E101" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -21481,30 +21695,30 @@
         <v>46009</v>
       </c>
       <c r="L101" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M101" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="B102" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C102" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D102" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E102" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="F102" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="J102">
         <v>2</v>
@@ -21513,33 +21727,33 @@
         <v>46233</v>
       </c>
       <c r="L102" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M102" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="B103" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C103" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D103" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="E103" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="F103" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="G103" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="J103">
         <v>3</v>
@@ -21548,24 +21762,24 @@
         <v>46233</v>
       </c>
       <c r="L103" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="B104" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="C104" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D104" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -21574,24 +21788,24 @@
         <v>46009</v>
       </c>
       <c r="L104" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M104" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="B105" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="C105" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D105" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -21600,27 +21814,27 @@
         <v>46009</v>
       </c>
       <c r="L105" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M105" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="B106" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C106" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D106" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E106" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J106">
         <v>1</v>
@@ -21629,27 +21843,27 @@
         <v>46009</v>
       </c>
       <c r="L106" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="B107" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C107" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D107" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E107" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J107">
         <v>1</v>
@@ -21658,27 +21872,27 @@
         <v>46009</v>
       </c>
       <c r="L107" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M107" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="B108" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C108" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D108" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E108" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -21687,27 +21901,27 @@
         <v>46009</v>
       </c>
       <c r="L108" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="B109" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C109" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D109" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E109" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -21716,27 +21930,27 @@
         <v>46009</v>
       </c>
       <c r="L109" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M109" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="B110" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="C110" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D110" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E110" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J110">
         <v>1</v>
@@ -21745,27 +21959,27 @@
         <v>46009</v>
       </c>
       <c r="L110" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M110" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="B111" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="C111" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D111" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E111" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J111">
         <v>1</v>
@@ -21774,27 +21988,27 @@
         <v>46009</v>
       </c>
       <c r="L111" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M111" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="B112" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="C112" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="D112" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E112" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -21803,27 +22017,27 @@
         <v>46009</v>
       </c>
       <c r="L112" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M112" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="B113" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="C113" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="D113" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E113" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="J113">
         <v>1</v>
@@ -21832,27 +22046,27 @@
         <v>46009</v>
       </c>
       <c r="L113" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M113" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="B114" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="C114" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D114" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E114" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -21861,36 +22075,36 @@
         <v>46009</v>
       </c>
       <c r="L114" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M114" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="B115" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C115" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D115" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E115" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="F115" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G115" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="H115" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="J115">
         <v>4</v>
@@ -21899,33 +22113,33 @@
         <v>46233</v>
       </c>
       <c r="L115" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M115" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="B116" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="C116" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D116" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E116" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="F116" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G116" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="J116">
         <v>3</v>
@@ -21934,27 +22148,27 @@
         <v>46170</v>
       </c>
       <c r="L116" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M116" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="B117" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="C117" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D117" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E117" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -21963,27 +22177,27 @@
         <v>46009</v>
       </c>
       <c r="L117" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M117" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="B118" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="C118" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D118" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E118" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -21992,27 +22206,27 @@
         <v>46009</v>
       </c>
       <c r="L118" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M118" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="B119" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="C119" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D119" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="E119" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -22021,27 +22235,27 @@
         <v>45968</v>
       </c>
       <c r="L119" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M119" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="B120" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="C120" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="D120" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="E120" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -22050,24 +22264,24 @@
         <v>45968</v>
       </c>
       <c r="L120" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M120" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="B121" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="C121" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D121" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -22076,30 +22290,30 @@
         <v>45968</v>
       </c>
       <c r="L121" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M121" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="B122" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="C122" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D122" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E122" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="F122" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="J122">
         <v>2</v>
@@ -22108,24 +22322,24 @@
         <v>46170</v>
       </c>
       <c r="L122" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M122" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="B123" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="C123" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D123" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -22134,24 +22348,24 @@
         <v>45968</v>
       </c>
       <c r="L123" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M123" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="B124" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="C124" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D124" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -22160,24 +22374,24 @@
         <v>45968</v>
       </c>
       <c r="L124" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M124" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="B125" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="C125" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D125" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -22186,24 +22400,24 @@
         <v>45968</v>
       </c>
       <c r="L125" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M125" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="B126" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="C126" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D126" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -22212,27 +22426,27 @@
         <v>45968</v>
       </c>
       <c r="L126" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M126" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="B127" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="C127" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D127" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E127" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="J127">
         <v>1</v>
@@ -22241,24 +22455,24 @@
         <v>46170</v>
       </c>
       <c r="L127" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M127" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="B128" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="C128" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D128" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -22267,24 +22481,24 @@
         <v>45968</v>
       </c>
       <c r="L128" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M128" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="B129" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="C129" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="D129" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -22293,10 +22507,10 @@
         <v>45968</v>
       </c>
       <c r="L129" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M129" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
@@ -23115,7 +23329,7 @@
         <v>449</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="42.75" x14ac:dyDescent="0.25">
@@ -23123,7 +23337,7 @@
         <v>450</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="71.25" x14ac:dyDescent="0.25">
@@ -23131,7 +23345,7 @@
         <v>451</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="142.5" x14ac:dyDescent="0.25">
@@ -23139,7 +23353,7 @@
         <v>452</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="99.75" x14ac:dyDescent="0.25">
@@ -23147,7 +23361,7 @@
         <v>453</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="114" x14ac:dyDescent="0.25">
@@ -23155,7 +23369,7 @@
         <v>454</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="213.75" x14ac:dyDescent="0.25">
@@ -23163,7 +23377,7 @@
         <v>455</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="142.5" x14ac:dyDescent="0.25">
@@ -23171,7 +23385,7 @@
         <v>456</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="199.5" x14ac:dyDescent="0.25">
@@ -23179,7 +23393,7 @@
         <v>457</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="57" x14ac:dyDescent="0.25">
@@ -23187,7 +23401,7 @@
         <v>458</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="99.75" x14ac:dyDescent="0.25">
@@ -23195,7 +23409,7 @@
         <v>459</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="228" x14ac:dyDescent="0.25">
@@ -23203,7 +23417,7 @@
         <v>460</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="185.25" x14ac:dyDescent="0.25">
@@ -23211,7 +23425,7 @@
         <v>461</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="342" x14ac:dyDescent="0.25">
@@ -23219,7 +23433,7 @@
         <v>462</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="114" x14ac:dyDescent="0.25">
@@ -23227,7 +23441,7 @@
         <v>463</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="128.25" x14ac:dyDescent="0.25">
@@ -23235,7 +23449,7 @@
         <v>464</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
@@ -23244,7 +23458,7 @@
       </c>
       <c r="C21" s="27">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
@@ -23263,72 +23477,72 @@
     </row>
     <row r="25" spans="2:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="29" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="C25" s="26"/>
     </row>
     <row r="26" spans="2:3" ht="114" x14ac:dyDescent="0.25">
       <c r="B26" s="25" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="99.75" x14ac:dyDescent="0.25">
       <c r="B27" s="25" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="99.75" x14ac:dyDescent="0.25">
       <c r="B28" s="25" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="128.25" x14ac:dyDescent="0.25">
       <c r="B29" s="25" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="171" x14ac:dyDescent="0.25">
       <c r="B30" s="25" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="99.75" x14ac:dyDescent="0.25">
       <c r="B31" s="25" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="85.5" x14ac:dyDescent="0.25">
       <c r="B32" s="25" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="142.5" x14ac:dyDescent="0.25">
       <c r="B33" s="25" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
@@ -23417,7 +23631,7 @@
       </c>
       <c r="C7" s="13">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -23597,7 +23811,7 @@
       </c>
       <c r="C31" s="4">
         <f>COUNTIF('Meeting Minutes Log'!I2:I299,"Open")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
@@ -23768,7 +23982,7 @@
       </c>
       <c r="C52" s="4">
         <f ca="1">COUNTIF('Submittal Log'!P2:P299,"&gt;=14")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
@@ -29731,19 +29945,19 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D2" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E2" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F2" s="24">
         <v>46268</v>
@@ -29758,14 +29972,14 @@
         <v>46289</v>
       </c>
       <c r="J2" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K65" ca="1" si="0">IF(A2="","",IF(I2&lt;&gt;"",I2-G2,IF(G2&lt;&gt;"",TODAY()-G2,"")))</f>
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="N2" t="s">
         <v>273</v>
@@ -29781,19 +29995,19 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D3" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E3" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F3" s="24">
         <v>46287</v>
@@ -29808,14 +30022,14 @@
         <v>46293</v>
       </c>
       <c r="J3" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="M3" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="N3" t="s">
         <v>273</v>
@@ -29831,19 +30045,19 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C4" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="D4" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="F4" s="24">
         <v>46260</v>
@@ -29858,14 +30072,14 @@
         <v>46296</v>
       </c>
       <c r="J4" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="N4" t="s">
         <v>273</v>
@@ -29876,24 +30090,24 @@
       </c>
       <c r="P4">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C5" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="D5" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E5" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F5" s="24">
         <v>46260</v>
@@ -29908,14 +30122,14 @@
         <v>46296</v>
       </c>
       <c r="J5" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="N5" t="s">
         <v>273</v>
@@ -29926,24 +30140,24 @@
       </c>
       <c r="P5">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C6" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="D6" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E6" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F6" s="24">
         <v>46260</v>
@@ -29958,14 +30172,14 @@
         <v>46296</v>
       </c>
       <c r="J6" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="N6" t="s">
         <v>273</v>
@@ -29976,24 +30190,24 @@
       </c>
       <c r="P6">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C7" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="D7" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E7" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F7" s="24">
         <v>46260</v>
@@ -30008,14 +30222,14 @@
         <v>46296</v>
       </c>
       <c r="J7" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="N7" t="s">
         <v>273</v>
@@ -30026,24 +30240,24 @@
       </c>
       <c r="P7">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C8" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="D8" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F8" s="24">
         <v>46260</v>
@@ -30058,14 +30272,14 @@
         <v>46296</v>
       </c>
       <c r="J8" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="0"/>
         <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="N8" t="s">
         <v>273</v>
@@ -30076,24 +30290,24 @@
       </c>
       <c r="P8">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C9" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="D9" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E9" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="F9" s="24">
         <v>46260</v>
@@ -30108,14 +30322,14 @@
         <v>46290</v>
       </c>
       <c r="J9" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="0"/>
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="N9" t="s">
         <v>273</v>
@@ -30131,19 +30345,19 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D10" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E10" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="F10" s="24">
         <v>46265</v>
@@ -30155,14 +30369,14 @@
         <v>46290</v>
       </c>
       <c r="J10" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="N10" t="s">
         <v>273</v>
@@ -30173,24 +30387,24 @@
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C11" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="D11" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="E11" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="F11" s="24">
         <v>46265</v>
@@ -30202,14 +30416,14 @@
         <v>46290</v>
       </c>
       <c r="J11" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="N11" t="s">
         <v>273</v>
@@ -30220,24 +30434,24 @@
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C12" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="D12" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="E12" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="F12" s="24">
         <v>46265</v>
@@ -30249,14 +30463,14 @@
         <v>46290</v>
       </c>
       <c r="J12" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="N12" t="s">
         <v>273</v>
@@ -30267,7 +30481,7 @@
       </c>
       <c r="P12">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -34385,19 +34599,19 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="B2" s="24">
         <v>46254</v>
       </c>
       <c r="C2" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D2" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E2" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="H2">
         <v>99986.52</v>
@@ -34406,14 +34620,14 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="M2">
         <f>IF(A2="","",SUMIFS(H$2:H2,J$2:J2,"Approved"))</f>
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="O2" t="s">
         <v>273</v>
@@ -34424,27 +34638,27 @@
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q65" ca="1" si="1">IF(A2="","",IF(OR(J2="Approved",J2="Rejected",J2="Void"),"",TODAY()-P2))</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="B3" s="24">
         <v>46259</v>
       </c>
       <c r="C3" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="D3" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E3" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -34453,14 +34667,14 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="M3">
         <f>IF(A3="","",SUMIFS(H$2:H3,J$2:J3,"Approved"))</f>
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="O3" t="s">
         <v>273</v>
@@ -34471,10 +34685,10 @@
       </c>
       <c r="Q3">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R3" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -38728,19 +38942,19 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="B2" s="24">
         <v>46257</v>
       </c>
       <c r="C2" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="F2">
         <v>56430</v>
@@ -38749,19 +38963,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="J2" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="K2" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="L2" s="24">
         <v>46296</v>
       </c>
       <c r="M2" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="N2">
         <v>56430</v>
@@ -38771,7 +38985,7 @@
         <v>56430</v>
       </c>
       <c r="P2" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="Q2" t="s">
         <v>273</v>
